--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648399</v>
+        <v>122648436</v>
       </c>
       <c r="B2" t="n">
-        <v>74749</v>
+        <v>79766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535550</v>
+        <v>535358</v>
       </c>
       <c r="R2" t="n">
-        <v>7264829</v>
+        <v>7264941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648483</v>
+        <v>122648474</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>82443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534458</v>
+        <v>534908</v>
       </c>
       <c r="R3" t="n">
         <v>7265138</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648456</v>
+        <v>122648483</v>
       </c>
       <c r="B4" t="n">
-        <v>91124</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535016</v>
+        <v>534458</v>
       </c>
       <c r="R4" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648428</v>
+        <v>122648461</v>
       </c>
       <c r="B5" t="n">
-        <v>90829</v>
+        <v>90851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534215</v>
+        <v>534980</v>
       </c>
       <c r="R5" t="n">
-        <v>7265115</v>
+        <v>7265114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648492</v>
+        <v>122648453</v>
       </c>
       <c r="B6" t="n">
-        <v>74757</v>
+        <v>91278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534466</v>
+        <v>535037</v>
       </c>
       <c r="R6" t="n">
-        <v>7265134</v>
+        <v>7265096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648427</v>
+        <v>122648465</v>
       </c>
       <c r="B7" t="n">
-        <v>74757</v>
+        <v>74569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534208</v>
+        <v>534361</v>
       </c>
       <c r="R7" t="n">
-        <v>7265114</v>
+        <v>7265171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648436</v>
+        <v>122648475</v>
       </c>
       <c r="B8" t="n">
-        <v>79766</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535358</v>
+        <v>534909</v>
       </c>
       <c r="R8" t="n">
-        <v>7264941</v>
+        <v>7265136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,6 +1389,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648417</v>
+        <v>122648478</v>
       </c>
       <c r="B9" t="n">
-        <v>91124</v>
+        <v>90851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535039</v>
+        <v>534371</v>
       </c>
       <c r="R9" t="n">
-        <v>7265098</v>
+        <v>7265136</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648475</v>
+        <v>122648399</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>74749</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534909</v>
+        <v>535550</v>
       </c>
       <c r="R10" t="n">
-        <v>7265136</v>
+        <v>7264829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,11 +1606,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648398</v>
+        <v>122648390</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>90847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535550</v>
+        <v>535573</v>
       </c>
       <c r="R11" t="n">
-        <v>7264828</v>
+        <v>7264817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648324</v>
+        <v>122648426</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>77603</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535921</v>
+        <v>534205</v>
       </c>
       <c r="R12" t="n">
-        <v>7264587</v>
+        <v>7265119</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648479</v>
+        <v>122648417</v>
       </c>
       <c r="B13" t="n">
-        <v>91771</v>
+        <v>91124</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534384</v>
+        <v>535039</v>
       </c>
       <c r="R13" t="n">
-        <v>7265135</v>
+        <v>7265098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648464</v>
+        <v>122648355</v>
       </c>
       <c r="B14" t="n">
-        <v>79772</v>
+        <v>90851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534978</v>
+        <v>535896</v>
       </c>
       <c r="R14" t="n">
-        <v>7265116</v>
+        <v>7264601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648390</v>
+        <v>122648492</v>
       </c>
       <c r="B15" t="n">
-        <v>90847</v>
+        <v>74757</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535573</v>
+        <v>534466</v>
       </c>
       <c r="R15" t="n">
-        <v>7264817</v>
+        <v>7265134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648426</v>
+        <v>122648479</v>
       </c>
       <c r="B16" t="n">
-        <v>77603</v>
+        <v>91771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534205</v>
+        <v>534384</v>
       </c>
       <c r="R16" t="n">
-        <v>7265119</v>
+        <v>7265135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648468</v>
+        <v>122648462</v>
       </c>
       <c r="B17" t="n">
-        <v>90847</v>
+        <v>91771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535007</v>
+        <v>534952</v>
       </c>
       <c r="R17" t="n">
         <v>7265120</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648461</v>
+        <v>122648398</v>
       </c>
       <c r="B18" t="n">
-        <v>90851</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534980</v>
+        <v>535550</v>
       </c>
       <c r="R18" t="n">
-        <v>7265114</v>
+        <v>7264828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648470</v>
+        <v>122648468</v>
       </c>
       <c r="B19" t="n">
-        <v>74762</v>
+        <v>90847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534374</v>
+        <v>535007</v>
       </c>
       <c r="R19" t="n">
-        <v>7265137</v>
+        <v>7265120</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648453</v>
+        <v>122648455</v>
       </c>
       <c r="B20" t="n">
         <v>91278</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535037</v>
+        <v>535016</v>
       </c>
       <c r="R20" t="n">
-        <v>7265096</v>
+        <v>7265112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648403</v>
+        <v>122648427</v>
       </c>
       <c r="B21" t="n">
-        <v>74741</v>
+        <v>74757</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534162</v>
+        <v>534208</v>
       </c>
       <c r="R21" t="n">
-        <v>7265113</v>
+        <v>7265114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648455</v>
+        <v>122648403</v>
       </c>
       <c r="B22" t="n">
-        <v>91278</v>
+        <v>74741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535016</v>
+        <v>534162</v>
       </c>
       <c r="R22" t="n">
-        <v>7265112</v>
+        <v>7265113</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648418</v>
+        <v>122648447</v>
       </c>
       <c r="B23" t="n">
-        <v>92147</v>
+        <v>90829</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534203</v>
+        <v>535157</v>
       </c>
       <c r="R23" t="n">
-        <v>7265101</v>
+        <v>7265060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3012,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648465</v>
+        <v>122648396</v>
       </c>
       <c r="B24" t="n">
-        <v>74569</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534361</v>
+        <v>534129</v>
       </c>
       <c r="R24" t="n">
-        <v>7265171</v>
+        <v>7265112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648478</v>
+        <v>122648467</v>
       </c>
       <c r="B25" t="n">
-        <v>90851</v>
+        <v>90829</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534371</v>
+        <v>534384</v>
       </c>
       <c r="R25" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3218,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3224,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648355</v>
+        <v>122648466</v>
       </c>
       <c r="B26" t="n">
-        <v>90851</v>
+        <v>74762</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3240,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535896</v>
+        <v>534360</v>
       </c>
       <c r="R26" t="n">
-        <v>7264601</v>
+        <v>7265163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648466</v>
+        <v>122648470</v>
       </c>
       <c r="B27" t="n">
         <v>74762</v>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534360</v>
+        <v>534374</v>
       </c>
       <c r="R27" t="n">
-        <v>7265163</v>
+        <v>7265137</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648462</v>
+        <v>122648428</v>
       </c>
       <c r="B28" t="n">
-        <v>91771</v>
+        <v>90829</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,25 +3453,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534952</v>
+        <v>534215</v>
       </c>
       <c r="R28" t="n">
-        <v>7265120</v>
+        <v>7265115</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3542,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648474</v>
+        <v>122648324</v>
       </c>
       <c r="B29" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534908</v>
+        <v>535921</v>
       </c>
       <c r="R29" t="n">
-        <v>7265138</v>
+        <v>7264587</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,7 +3642,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3648,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648467</v>
+        <v>122648456</v>
       </c>
       <c r="B30" t="n">
-        <v>90829</v>
+        <v>91124</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3664,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3688,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R30" t="n">
-        <v>7265120</v>
+        <v>7265101</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3754,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648447</v>
+        <v>122648464</v>
       </c>
       <c r="B31" t="n">
-        <v>90829</v>
+        <v>79772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3766,25 +3771,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3794,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535157</v>
+        <v>534978</v>
       </c>
       <c r="R31" t="n">
-        <v>7265060</v>
+        <v>7265116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648396</v>
+        <v>122648418</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>92147</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3872,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534129</v>
+        <v>534203</v>
       </c>
       <c r="R32" t="n">
-        <v>7265112</v>
+        <v>7265101</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,11 +3941,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648436</v>
+        <v>122648427</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>74758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535358</v>
+        <v>534208</v>
       </c>
       <c r="R2" t="n">
-        <v>7264941</v>
+        <v>7265114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648474</v>
+        <v>122648426</v>
       </c>
       <c r="B3" t="n">
-        <v>82443</v>
+        <v>77604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534908</v>
+        <v>534205</v>
       </c>
       <c r="R3" t="n">
-        <v>7265138</v>
+        <v>7265119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648483</v>
+        <v>122648418</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>92148</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534458</v>
+        <v>534203</v>
       </c>
       <c r="R4" t="n">
-        <v>7265138</v>
+        <v>7265101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648461</v>
+        <v>122648474</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>82444</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534980</v>
+        <v>534908</v>
       </c>
       <c r="R5" t="n">
-        <v>7265114</v>
+        <v>7265138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648453</v>
+        <v>122648403</v>
       </c>
       <c r="B6" t="n">
-        <v>91278</v>
+        <v>74742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535037</v>
+        <v>534162</v>
       </c>
       <c r="R6" t="n">
-        <v>7265096</v>
+        <v>7265113</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648465</v>
+        <v>122648447</v>
       </c>
       <c r="B7" t="n">
-        <v>74569</v>
+        <v>90830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534361</v>
+        <v>535157</v>
       </c>
       <c r="R7" t="n">
-        <v>7265171</v>
+        <v>7265060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648475</v>
+        <v>122648464</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>79773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534909</v>
+        <v>534978</v>
       </c>
       <c r="R8" t="n">
-        <v>7265136</v>
+        <v>7265116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1389,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648478</v>
+        <v>122648479</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>91772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534371</v>
+        <v>534384</v>
       </c>
       <c r="R9" t="n">
-        <v>7265136</v>
+        <v>7265135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648399</v>
+        <v>122648455</v>
       </c>
       <c r="B10" t="n">
-        <v>74749</v>
+        <v>91279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535550</v>
+        <v>535016</v>
       </c>
       <c r="R10" t="n">
-        <v>7264829</v>
+        <v>7265112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648390</v>
+        <v>122648436</v>
       </c>
       <c r="B11" t="n">
-        <v>90847</v>
+        <v>79767</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535573</v>
+        <v>535358</v>
       </c>
       <c r="R11" t="n">
-        <v>7264817</v>
+        <v>7264941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648426</v>
+        <v>122648483</v>
       </c>
       <c r="B12" t="n">
-        <v>77603</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534205</v>
+        <v>534458</v>
       </c>
       <c r="R12" t="n">
-        <v>7265119</v>
+        <v>7265138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648417</v>
+        <v>122648466</v>
       </c>
       <c r="B13" t="n">
-        <v>91124</v>
+        <v>74763</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535039</v>
+        <v>534360</v>
       </c>
       <c r="R13" t="n">
-        <v>7265098</v>
+        <v>7265163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648355</v>
+        <v>122648475</v>
       </c>
       <c r="B14" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535896</v>
+        <v>534909</v>
       </c>
       <c r="R14" t="n">
-        <v>7264601</v>
+        <v>7265136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2025,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648492</v>
+        <v>122648467</v>
       </c>
       <c r="B15" t="n">
-        <v>74757</v>
+        <v>90830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534466</v>
+        <v>534384</v>
       </c>
       <c r="R15" t="n">
-        <v>7265134</v>
+        <v>7265120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648479</v>
+        <v>122648355</v>
       </c>
       <c r="B16" t="n">
-        <v>91771</v>
+        <v>90852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534384</v>
+        <v>535896</v>
       </c>
       <c r="R16" t="n">
-        <v>7265135</v>
+        <v>7264601</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648462</v>
+        <v>122648453</v>
       </c>
       <c r="B17" t="n">
-        <v>91771</v>
+        <v>91279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534952</v>
+        <v>535037</v>
       </c>
       <c r="R17" t="n">
-        <v>7265120</v>
+        <v>7265096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648398</v>
+        <v>122648399</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>74750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>535550</v>
       </c>
       <c r="R18" t="n">
-        <v>7264828</v>
+        <v>7264829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648468</v>
+        <v>122648390</v>
       </c>
       <c r="B19" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535007</v>
+        <v>535573</v>
       </c>
       <c r="R19" t="n">
-        <v>7265120</v>
+        <v>7264817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648455</v>
+        <v>122648428</v>
       </c>
       <c r="B20" t="n">
-        <v>91278</v>
+        <v>90830</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535016</v>
+        <v>534215</v>
       </c>
       <c r="R20" t="n">
-        <v>7265112</v>
+        <v>7265115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648427</v>
+        <v>122648478</v>
       </c>
       <c r="B21" t="n">
-        <v>74757</v>
+        <v>90852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534208</v>
+        <v>534371</v>
       </c>
       <c r="R21" t="n">
-        <v>7265114</v>
+        <v>7265136</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648403</v>
+        <v>122648456</v>
       </c>
       <c r="B22" t="n">
-        <v>74741</v>
+        <v>91125</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534162</v>
+        <v>535016</v>
       </c>
       <c r="R22" t="n">
-        <v>7265113</v>
+        <v>7265101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648447</v>
+        <v>122648470</v>
       </c>
       <c r="B23" t="n">
-        <v>90829</v>
+        <v>74763</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535157</v>
+        <v>534374</v>
       </c>
       <c r="R23" t="n">
-        <v>7265060</v>
+        <v>7265137</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3012,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648396</v>
+        <v>122648417</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>91125</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,21 +3028,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534129</v>
+        <v>535039</v>
       </c>
       <c r="R24" t="n">
-        <v>7265112</v>
+        <v>7265098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,11 +3090,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3123,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648467</v>
+        <v>122648396</v>
       </c>
       <c r="B25" t="n">
-        <v>90829</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534384</v>
+        <v>534129</v>
       </c>
       <c r="R25" t="n">
-        <v>7265120</v>
+        <v>7265112</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,6 +3196,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3229,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648466</v>
+        <v>122648468</v>
       </c>
       <c r="B26" t="n">
-        <v>74762</v>
+        <v>90848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3245,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534360</v>
+        <v>535007</v>
       </c>
       <c r="R26" t="n">
-        <v>7265163</v>
+        <v>7265120</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648470</v>
+        <v>122648462</v>
       </c>
       <c r="B27" t="n">
-        <v>74762</v>
+        <v>91772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534374</v>
+        <v>534952</v>
       </c>
       <c r="R27" t="n">
-        <v>7265137</v>
+        <v>7265120</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3441,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648428</v>
+        <v>122648398</v>
       </c>
       <c r="B28" t="n">
-        <v>90829</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,25 +3453,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534215</v>
+        <v>535550</v>
       </c>
       <c r="R28" t="n">
-        <v>7265115</v>
+        <v>7264828</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648324</v>
+        <v>122648461</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535921</v>
+        <v>534980</v>
       </c>
       <c r="R29" t="n">
-        <v>7264587</v>
+        <v>7265114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648456</v>
+        <v>122648465</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>74570</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3665,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535016</v>
+        <v>534361</v>
       </c>
       <c r="R30" t="n">
-        <v>7265101</v>
+        <v>7265171</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648464</v>
+        <v>122648324</v>
       </c>
       <c r="B31" t="n">
-        <v>79772</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,20 +3771,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534978</v>
+        <v>535921</v>
       </c>
       <c r="R31" t="n">
-        <v>7265116</v>
+        <v>7264587</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648418</v>
+        <v>122648492</v>
       </c>
       <c r="B32" t="n">
-        <v>92147</v>
+        <v>74758</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534203</v>
+        <v>534466</v>
       </c>
       <c r="R32" t="n">
-        <v>7265101</v>
+        <v>7265134</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648418</v>
+        <v>122648474</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>82444</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534203</v>
+        <v>534908</v>
       </c>
       <c r="R4" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648474</v>
+        <v>122648403</v>
       </c>
       <c r="B5" t="n">
-        <v>82444</v>
+        <v>74742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534908</v>
+        <v>534162</v>
       </c>
       <c r="R5" t="n">
-        <v>7265138</v>
+        <v>7265113</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648403</v>
+        <v>122648418</v>
       </c>
       <c r="B6" t="n">
-        <v>74742</v>
+        <v>92148</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534162</v>
+        <v>534203</v>
       </c>
       <c r="R6" t="n">
-        <v>7265113</v>
+        <v>7265101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648483</v>
+        <v>122648466</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>74763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534458</v>
+        <v>534360</v>
       </c>
       <c r="R12" t="n">
-        <v>7265138</v>
+        <v>7265163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648466</v>
+        <v>122648483</v>
       </c>
       <c r="B13" t="n">
-        <v>74763</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534360</v>
+        <v>534458</v>
       </c>
       <c r="R13" t="n">
-        <v>7265163</v>
+        <v>7265138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648396</v>
+        <v>122648468</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>90848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534129</v>
+        <v>535007</v>
       </c>
       <c r="R25" t="n">
-        <v>7265112</v>
+        <v>7265120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,11 +3196,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3218,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3229,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648468</v>
+        <v>122648462</v>
       </c>
       <c r="B26" t="n">
-        <v>90848</v>
+        <v>91772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,7 +3264,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535007</v>
+        <v>534952</v>
       </c>
       <c r="R26" t="n">
         <v>7265120</v>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648462</v>
+        <v>122648396</v>
       </c>
       <c r="B27" t="n">
-        <v>91772</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534952</v>
+        <v>534129</v>
       </c>
       <c r="R27" t="n">
-        <v>7265120</v>
+        <v>7265112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648427</v>
+        <v>122648390</v>
       </c>
       <c r="B2" t="n">
-        <v>74758</v>
+        <v>90851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534208</v>
+        <v>535573</v>
       </c>
       <c r="R2" t="n">
-        <v>7265114</v>
+        <v>7264817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648426</v>
+        <v>122648453</v>
       </c>
       <c r="B3" t="n">
-        <v>77604</v>
+        <v>91282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534205</v>
+        <v>535037</v>
       </c>
       <c r="R3" t="n">
-        <v>7265119</v>
+        <v>7265096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648474</v>
+        <v>122648418</v>
       </c>
       <c r="B4" t="n">
-        <v>82444</v>
+        <v>92151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534908</v>
+        <v>534203</v>
       </c>
       <c r="R4" t="n">
-        <v>7265138</v>
+        <v>7265101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648403</v>
+        <v>122648447</v>
       </c>
       <c r="B5" t="n">
-        <v>74742</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534162</v>
+        <v>535157</v>
       </c>
       <c r="R5" t="n">
-        <v>7265113</v>
+        <v>7265060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648418</v>
+        <v>122648474</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>82447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534203</v>
+        <v>534908</v>
       </c>
       <c r="R6" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648447</v>
+        <v>122648467</v>
       </c>
       <c r="B7" t="n">
-        <v>90830</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535157</v>
+        <v>534384</v>
       </c>
       <c r="R7" t="n">
-        <v>7265060</v>
+        <v>7265120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648464</v>
+        <v>122648426</v>
       </c>
       <c r="B8" t="n">
-        <v>79773</v>
+        <v>77607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534978</v>
+        <v>534205</v>
       </c>
       <c r="R8" t="n">
-        <v>7265116</v>
+        <v>7265119</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648479</v>
+        <v>122648470</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>74766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534384</v>
+        <v>534374</v>
       </c>
       <c r="R9" t="n">
-        <v>7265135</v>
+        <v>7265137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648455</v>
+        <v>122648436</v>
       </c>
       <c r="B10" t="n">
-        <v>91279</v>
+        <v>79770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535016</v>
+        <v>535358</v>
       </c>
       <c r="R10" t="n">
-        <v>7265112</v>
+        <v>7264941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648436</v>
+        <v>122648417</v>
       </c>
       <c r="B11" t="n">
-        <v>79767</v>
+        <v>91128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535358</v>
+        <v>535039</v>
       </c>
       <c r="R11" t="n">
-        <v>7264941</v>
+        <v>7265098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648466</v>
+        <v>122648455</v>
       </c>
       <c r="B12" t="n">
-        <v>74763</v>
+        <v>91282</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534360</v>
+        <v>535016</v>
       </c>
       <c r="R12" t="n">
-        <v>7265163</v>
+        <v>7265112</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1844,7 +1844,7 @@
         <v>122648483</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648475</v>
+        <v>122648478</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534909</v>
+        <v>534371</v>
       </c>
       <c r="R14" t="n">
         <v>7265136</v>
@@ -2025,11 +2025,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648467</v>
+        <v>122648396</v>
       </c>
       <c r="B15" t="n">
-        <v>90830</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534384</v>
+        <v>534129</v>
       </c>
       <c r="R15" t="n">
-        <v>7265120</v>
+        <v>7265112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,6 +2131,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648355</v>
+        <v>122648428</v>
       </c>
       <c r="B16" t="n">
-        <v>90852</v>
+        <v>90833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535896</v>
+        <v>534215</v>
       </c>
       <c r="R16" t="n">
-        <v>7264601</v>
+        <v>7265115</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648453</v>
+        <v>122648479</v>
       </c>
       <c r="B17" t="n">
-        <v>91279</v>
+        <v>91775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535037</v>
+        <v>534384</v>
       </c>
       <c r="R17" t="n">
-        <v>7265096</v>
+        <v>7265135</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648399</v>
+        <v>122648398</v>
       </c>
       <c r="B18" t="n">
-        <v>74750</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>535550</v>
       </c>
       <c r="R18" t="n">
-        <v>7264829</v>
+        <v>7264828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648390</v>
+        <v>122648492</v>
       </c>
       <c r="B19" t="n">
-        <v>90848</v>
+        <v>74761</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535573</v>
+        <v>534466</v>
       </c>
       <c r="R19" t="n">
-        <v>7264817</v>
+        <v>7265134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648428</v>
+        <v>122648475</v>
       </c>
       <c r="B20" t="n">
-        <v>90830</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534215</v>
+        <v>534909</v>
       </c>
       <c r="R20" t="n">
-        <v>7265115</v>
+        <v>7265136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,6 +2666,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2683,7 +2688,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648478</v>
+        <v>122648403</v>
       </c>
       <c r="B21" t="n">
-        <v>90852</v>
+        <v>74745</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534371</v>
+        <v>534162</v>
       </c>
       <c r="R21" t="n">
-        <v>7265136</v>
+        <v>7265113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648456</v>
+        <v>122648462</v>
       </c>
       <c r="B22" t="n">
-        <v>91125</v>
+        <v>91775</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535016</v>
+        <v>534952</v>
       </c>
       <c r="R22" t="n">
-        <v>7265101</v>
+        <v>7265120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648470</v>
+        <v>122648324</v>
       </c>
       <c r="B23" t="n">
-        <v>74763</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2927,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534374</v>
+        <v>535921</v>
       </c>
       <c r="R23" t="n">
-        <v>7265137</v>
+        <v>7264587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3012,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648417</v>
+        <v>122648464</v>
       </c>
       <c r="B24" t="n">
-        <v>91125</v>
+        <v>79776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3029,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535039</v>
+        <v>534978</v>
       </c>
       <c r="R24" t="n">
-        <v>7265098</v>
+        <v>7265116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3118,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648468</v>
+        <v>122648456</v>
       </c>
       <c r="B25" t="n">
-        <v>90848</v>
+        <v>91128</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535007</v>
+        <v>535016</v>
       </c>
       <c r="R25" t="n">
-        <v>7265120</v>
+        <v>7265101</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3218,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3224,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648462</v>
+        <v>122648466</v>
       </c>
       <c r="B26" t="n">
-        <v>91772</v>
+        <v>74766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3241,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534952</v>
+        <v>534360</v>
       </c>
       <c r="R26" t="n">
-        <v>7265120</v>
+        <v>7265163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648396</v>
+        <v>122648465</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>74573</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534129</v>
+        <v>534361</v>
       </c>
       <c r="R27" t="n">
-        <v>7265112</v>
+        <v>7265171</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,11 +3411,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648398</v>
+        <v>122648468</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>90851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,25 +3453,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535550</v>
+        <v>535007</v>
       </c>
       <c r="R28" t="n">
-        <v>7264828</v>
+        <v>7265120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648461</v>
+        <v>122648427</v>
       </c>
       <c r="B29" t="n">
-        <v>90852</v>
+        <v>74761</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534980</v>
+        <v>534208</v>
       </c>
       <c r="R29" t="n">
         <v>7265114</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648465</v>
+        <v>122648399</v>
       </c>
       <c r="B30" t="n">
-        <v>74570</v>
+        <v>74753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3665,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534361</v>
+        <v>535550</v>
       </c>
       <c r="R30" t="n">
-        <v>7265171</v>
+        <v>7264829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648324</v>
+        <v>122648355</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535921</v>
+        <v>535896</v>
       </c>
       <c r="R31" t="n">
-        <v>7264587</v>
+        <v>7264601</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648492</v>
+        <v>122648461</v>
       </c>
       <c r="B32" t="n">
-        <v>74758</v>
+        <v>90855</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534466</v>
+        <v>534980</v>
       </c>
       <c r="R32" t="n">
-        <v>7265134</v>
+        <v>7265114</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648390</v>
+        <v>122648492</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>74761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535573</v>
+        <v>534466</v>
       </c>
       <c r="R2" t="n">
-        <v>7264817</v>
+        <v>7265134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648453</v>
+        <v>122648403</v>
       </c>
       <c r="B3" t="n">
-        <v>91282</v>
+        <v>74745</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535037</v>
+        <v>534162</v>
       </c>
       <c r="R3" t="n">
-        <v>7265096</v>
+        <v>7265113</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648418</v>
+        <v>122648462</v>
       </c>
       <c r="B4" t="n">
-        <v>92151</v>
+        <v>91775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534203</v>
+        <v>534952</v>
       </c>
       <c r="R4" t="n">
-        <v>7265101</v>
+        <v>7265120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648474</v>
+        <v>122648436</v>
       </c>
       <c r="B6" t="n">
-        <v>82447</v>
+        <v>79770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534908</v>
+        <v>535358</v>
       </c>
       <c r="R6" t="n">
-        <v>7265138</v>
+        <v>7264941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648467</v>
+        <v>122648390</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534384</v>
+        <v>535573</v>
       </c>
       <c r="R7" t="n">
-        <v>7265120</v>
+        <v>7264817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648426</v>
+        <v>122648465</v>
       </c>
       <c r="B8" t="n">
-        <v>77607</v>
+        <v>74573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534205</v>
+        <v>534361</v>
       </c>
       <c r="R8" t="n">
-        <v>7265119</v>
+        <v>7265171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648470</v>
+        <v>122648417</v>
       </c>
       <c r="B9" t="n">
-        <v>74766</v>
+        <v>91128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534374</v>
+        <v>535039</v>
       </c>
       <c r="R9" t="n">
-        <v>7265137</v>
+        <v>7265098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648436</v>
+        <v>122648456</v>
       </c>
       <c r="B10" t="n">
-        <v>79770</v>
+        <v>91128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535358</v>
+        <v>535016</v>
       </c>
       <c r="R10" t="n">
-        <v>7264941</v>
+        <v>7265101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648417</v>
+        <v>122648399</v>
       </c>
       <c r="B11" t="n">
-        <v>91128</v>
+        <v>74753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535039</v>
+        <v>535550</v>
       </c>
       <c r="R11" t="n">
-        <v>7265098</v>
+        <v>7264829</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648455</v>
+        <v>122648483</v>
       </c>
       <c r="B12" t="n">
-        <v>91282</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535016</v>
+        <v>534458</v>
       </c>
       <c r="R12" t="n">
-        <v>7265112</v>
+        <v>7265138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648483</v>
+        <v>122648474</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>82447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534458</v>
+        <v>534908</v>
       </c>
       <c r="R13" t="n">
         <v>7265138</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648478</v>
+        <v>122648467</v>
       </c>
       <c r="B14" t="n">
-        <v>90855</v>
+        <v>90833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534371</v>
+        <v>534384</v>
       </c>
       <c r="R14" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648396</v>
+        <v>122648461</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534129</v>
+        <v>534980</v>
       </c>
       <c r="R15" t="n">
-        <v>7265112</v>
+        <v>7265114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,11 +2131,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2153,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648479</v>
+        <v>122648453</v>
       </c>
       <c r="B17" t="n">
-        <v>91775</v>
+        <v>91282</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534384</v>
+        <v>535037</v>
       </c>
       <c r="R17" t="n">
-        <v>7265135</v>
+        <v>7265096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648398</v>
+        <v>122648355</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>90855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535550</v>
+        <v>535896</v>
       </c>
       <c r="R18" t="n">
-        <v>7264828</v>
+        <v>7264601</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648492</v>
+        <v>122648470</v>
       </c>
       <c r="B19" t="n">
-        <v>74761</v>
+        <v>74766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534466</v>
+        <v>534374</v>
       </c>
       <c r="R19" t="n">
-        <v>7265134</v>
+        <v>7265137</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648475</v>
+        <v>122648398</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>8430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534909</v>
+        <v>535550</v>
       </c>
       <c r="R20" t="n">
-        <v>7265136</v>
+        <v>7264828</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,11 +2661,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2688,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648403</v>
+        <v>122648455</v>
       </c>
       <c r="B21" t="n">
-        <v>74745</v>
+        <v>91282</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534162</v>
+        <v>535016</v>
       </c>
       <c r="R21" t="n">
-        <v>7265113</v>
+        <v>7265112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2805,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648462</v>
+        <v>122648479</v>
       </c>
       <c r="B22" t="n">
         <v>91775</v>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534952</v>
+        <v>534384</v>
       </c>
       <c r="R22" t="n">
-        <v>7265120</v>
+        <v>7265135</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2911,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648324</v>
+        <v>122648466</v>
       </c>
       <c r="B23" t="n">
-        <v>78660</v>
+        <v>74766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535921</v>
+        <v>534360</v>
       </c>
       <c r="R23" t="n">
-        <v>7264587</v>
+        <v>7265163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,7 +2996,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3017,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648464</v>
+        <v>122648475</v>
       </c>
       <c r="B24" t="n">
-        <v>79776</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534978</v>
+        <v>534909</v>
       </c>
       <c r="R24" t="n">
-        <v>7265116</v>
+        <v>7265136</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,6 +3085,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3123,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648456</v>
+        <v>122648426</v>
       </c>
       <c r="B25" t="n">
-        <v>91128</v>
+        <v>77607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535016</v>
+        <v>534205</v>
       </c>
       <c r="R25" t="n">
-        <v>7265101</v>
+        <v>7265119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3229,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648466</v>
+        <v>122648468</v>
       </c>
       <c r="B26" t="n">
-        <v>74766</v>
+        <v>90851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3245,21 +3240,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534360</v>
+        <v>535007</v>
       </c>
       <c r="R26" t="n">
-        <v>7265163</v>
+        <v>7265120</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648465</v>
+        <v>122648418</v>
       </c>
       <c r="B27" t="n">
-        <v>74573</v>
+        <v>92151</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534361</v>
+        <v>534203</v>
       </c>
       <c r="R27" t="n">
-        <v>7265171</v>
+        <v>7265101</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648468</v>
+        <v>122648396</v>
       </c>
       <c r="B28" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,21 +3452,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535007</v>
+        <v>534129</v>
       </c>
       <c r="R28" t="n">
-        <v>7265120</v>
+        <v>7265112</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,6 +3514,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648427</v>
+        <v>122648478</v>
       </c>
       <c r="B29" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534208</v>
+        <v>534371</v>
       </c>
       <c r="R29" t="n">
-        <v>7265114</v>
+        <v>7265136</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648399</v>
+        <v>122648324</v>
       </c>
       <c r="B30" t="n">
-        <v>74753</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535550</v>
+        <v>535921</v>
       </c>
       <c r="R30" t="n">
-        <v>7264829</v>
+        <v>7264587</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648355</v>
+        <v>122648427</v>
       </c>
       <c r="B31" t="n">
-        <v>90855</v>
+        <v>74761</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535896</v>
+        <v>534208</v>
       </c>
       <c r="R31" t="n">
-        <v>7264601</v>
+        <v>7265114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648461</v>
+        <v>122648464</v>
       </c>
       <c r="B32" t="n">
-        <v>90855</v>
+        <v>79776</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534980</v>
+        <v>534978</v>
       </c>
       <c r="R32" t="n">
-        <v>7265114</v>
+        <v>7265116</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648470</v>
+        <v>122648398</v>
       </c>
       <c r="B19" t="n">
-        <v>74766</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534374</v>
+        <v>535550</v>
       </c>
       <c r="R19" t="n">
-        <v>7265137</v>
+        <v>7264828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648398</v>
+        <v>122648470</v>
       </c>
       <c r="B20" t="n">
-        <v>8430</v>
+        <v>74766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535550</v>
+        <v>534374</v>
       </c>
       <c r="R20" t="n">
-        <v>7264828</v>
+        <v>7265137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648398</v>
+        <v>122648470</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>74766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535550</v>
+        <v>534374</v>
       </c>
       <c r="R19" t="n">
-        <v>7264828</v>
+        <v>7265137</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648470</v>
+        <v>122648398</v>
       </c>
       <c r="B20" t="n">
-        <v>74766</v>
+        <v>8430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534374</v>
+        <v>535550</v>
       </c>
       <c r="R20" t="n">
-        <v>7265137</v>
+        <v>7264828</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648475</v>
+        <v>122648426</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
+        <v>77607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534909</v>
+        <v>534205</v>
       </c>
       <c r="R24" t="n">
-        <v>7265136</v>
+        <v>7265119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3085,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3107,7 +3102,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3118,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648426</v>
+        <v>122648475</v>
       </c>
       <c r="B25" t="n">
-        <v>77607</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534205</v>
+        <v>534909</v>
       </c>
       <c r="R25" t="n">
-        <v>7265119</v>
+        <v>7265136</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,6 +3191,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648470</v>
+        <v>122648398</v>
       </c>
       <c r="B19" t="n">
-        <v>74766</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534374</v>
+        <v>535550</v>
       </c>
       <c r="R19" t="n">
-        <v>7265137</v>
+        <v>7264828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648398</v>
+        <v>122648470</v>
       </c>
       <c r="B20" t="n">
-        <v>8430</v>
+        <v>74766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535550</v>
+        <v>534374</v>
       </c>
       <c r="R20" t="n">
-        <v>7264828</v>
+        <v>7265137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648426</v>
+        <v>122648475</v>
       </c>
       <c r="B24" t="n">
-        <v>77607</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534205</v>
+        <v>534909</v>
       </c>
       <c r="R24" t="n">
-        <v>7265119</v>
+        <v>7265136</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,6 +3085,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3102,7 +3107,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3113,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648475</v>
+        <v>122648426</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>77607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534909</v>
+        <v>534205</v>
       </c>
       <c r="R25" t="n">
-        <v>7265136</v>
+        <v>7265119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,11 +3196,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648478</v>
+        <v>122648427</v>
       </c>
       <c r="B29" t="n">
-        <v>90855</v>
+        <v>74761</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534371</v>
+        <v>534208</v>
       </c>
       <c r="R29" t="n">
-        <v>7265136</v>
+        <v>7265114</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648324</v>
+        <v>122648464</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>79776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,20 +3665,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535921</v>
+        <v>534978</v>
       </c>
       <c r="R30" t="n">
-        <v>7264587</v>
+        <v>7265116</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648427</v>
+        <v>122648478</v>
       </c>
       <c r="B31" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534208</v>
+        <v>534371</v>
       </c>
       <c r="R31" t="n">
-        <v>7265114</v>
+        <v>7265136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648464</v>
+        <v>122648324</v>
       </c>
       <c r="B32" t="n">
-        <v>79776</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,20 +3877,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534978</v>
+        <v>535921</v>
       </c>
       <c r="R32" t="n">
-        <v>7265116</v>
+        <v>7264587</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648475</v>
+        <v>122648426</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
+        <v>77607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534909</v>
+        <v>534205</v>
       </c>
       <c r="R24" t="n">
-        <v>7265136</v>
+        <v>7265119</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,11 +3085,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3107,7 +3102,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3118,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648426</v>
+        <v>122648475</v>
       </c>
       <c r="B25" t="n">
-        <v>77607</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534205</v>
+        <v>534909</v>
       </c>
       <c r="R25" t="n">
-        <v>7265119</v>
+        <v>7265136</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,6 +3191,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648398</v>
+        <v>122648470</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>74766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535550</v>
+        <v>534374</v>
       </c>
       <c r="R19" t="n">
-        <v>7264828</v>
+        <v>7265137</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648470</v>
+        <v>122648398</v>
       </c>
       <c r="B20" t="n">
-        <v>74766</v>
+        <v>8430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534374</v>
+        <v>535550</v>
       </c>
       <c r="R20" t="n">
-        <v>7265137</v>
+        <v>7264828</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648426</v>
+        <v>122648475</v>
       </c>
       <c r="B24" t="n">
-        <v>77607</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534205</v>
+        <v>534909</v>
       </c>
       <c r="R24" t="n">
-        <v>7265119</v>
+        <v>7265136</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,6 +3085,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3102,7 +3107,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3113,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648475</v>
+        <v>122648426</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
+        <v>77607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534909</v>
+        <v>534205</v>
       </c>
       <c r="R25" t="n">
-        <v>7265136</v>
+        <v>7265119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,11 +3196,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648492</v>
+        <v>122648466</v>
       </c>
       <c r="B2" t="n">
-        <v>74761</v>
+        <v>74868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534466</v>
+        <v>534360</v>
       </c>
       <c r="R2" t="n">
-        <v>7265134</v>
+        <v>7265163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648403</v>
+        <v>122648467</v>
       </c>
       <c r="B3" t="n">
-        <v>74745</v>
+        <v>90936</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534162</v>
+        <v>534384</v>
       </c>
       <c r="R3" t="n">
-        <v>7265113</v>
+        <v>7265120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>122648462</v>
       </c>
       <c r="B4" t="n">
-        <v>91775</v>
+        <v>91878</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648447</v>
+        <v>122648427</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535157</v>
+        <v>534208</v>
       </c>
       <c r="R5" t="n">
-        <v>7265060</v>
+        <v>7265114</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648436</v>
+        <v>122648478</v>
       </c>
       <c r="B6" t="n">
-        <v>79770</v>
+        <v>90958</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535358</v>
+        <v>534371</v>
       </c>
       <c r="R6" t="n">
-        <v>7264941</v>
+        <v>7265136</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648390</v>
+        <v>122648470</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>74868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535573</v>
+        <v>534374</v>
       </c>
       <c r="R7" t="n">
-        <v>7264817</v>
+        <v>7265137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648465</v>
+        <v>122648396</v>
       </c>
       <c r="B8" t="n">
-        <v>74573</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534361</v>
+        <v>534129</v>
       </c>
       <c r="R8" t="n">
-        <v>7265171</v>
+        <v>7265112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648417</v>
+        <v>122648324</v>
       </c>
       <c r="B9" t="n">
-        <v>91128</v>
+        <v>78762</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535039</v>
+        <v>535921</v>
       </c>
       <c r="R9" t="n">
-        <v>7265098</v>
+        <v>7264587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648456</v>
+        <v>122648474</v>
       </c>
       <c r="B10" t="n">
-        <v>91128</v>
+        <v>82549</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535016</v>
+        <v>534908</v>
       </c>
       <c r="R10" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648399</v>
+        <v>122648492</v>
       </c>
       <c r="B11" t="n">
-        <v>74753</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535550</v>
+        <v>534466</v>
       </c>
       <c r="R11" t="n">
-        <v>7264829</v>
+        <v>7265134</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648483</v>
+        <v>122648465</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>74675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534458</v>
+        <v>534361</v>
       </c>
       <c r="R12" t="n">
-        <v>7265138</v>
+        <v>7265171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648474</v>
+        <v>122648426</v>
       </c>
       <c r="B13" t="n">
-        <v>82447</v>
+        <v>77709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534908</v>
+        <v>534205</v>
       </c>
       <c r="R13" t="n">
-        <v>7265138</v>
+        <v>7265119</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648467</v>
+        <v>122648455</v>
       </c>
       <c r="B14" t="n">
-        <v>90833</v>
+        <v>91385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R14" t="n">
-        <v>7265120</v>
+        <v>7265112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648461</v>
+        <v>122648453</v>
       </c>
       <c r="B15" t="n">
-        <v>90855</v>
+        <v>91385</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534980</v>
+        <v>535037</v>
       </c>
       <c r="R15" t="n">
-        <v>7265114</v>
+        <v>7265096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648428</v>
+        <v>122648447</v>
       </c>
       <c r="B16" t="n">
-        <v>90833</v>
+        <v>90936</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534215</v>
+        <v>535157</v>
       </c>
       <c r="R16" t="n">
-        <v>7265115</v>
+        <v>7265060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648453</v>
+        <v>122648483</v>
       </c>
       <c r="B17" t="n">
-        <v>91282</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535037</v>
+        <v>534458</v>
       </c>
       <c r="R17" t="n">
-        <v>7265096</v>
+        <v>7265138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648355</v>
+        <v>122648399</v>
       </c>
       <c r="B18" t="n">
-        <v>90855</v>
+        <v>74855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535896</v>
+        <v>535550</v>
       </c>
       <c r="R18" t="n">
-        <v>7264601</v>
+        <v>7264829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648470</v>
+        <v>122648428</v>
       </c>
       <c r="B19" t="n">
-        <v>74766</v>
+        <v>90936</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534374</v>
+        <v>534215</v>
       </c>
       <c r="R19" t="n">
-        <v>7265137</v>
+        <v>7265115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648398</v>
+        <v>122648456</v>
       </c>
       <c r="B20" t="n">
-        <v>8430</v>
+        <v>91231</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535550</v>
+        <v>535016</v>
       </c>
       <c r="R20" t="n">
-        <v>7264828</v>
+        <v>7265101</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648455</v>
+        <v>122648418</v>
       </c>
       <c r="B21" t="n">
-        <v>91282</v>
+        <v>92254</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535016</v>
+        <v>534203</v>
       </c>
       <c r="R21" t="n">
-        <v>7265112</v>
+        <v>7265101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648479</v>
+        <v>122648464</v>
       </c>
       <c r="B22" t="n">
-        <v>91775</v>
+        <v>79878</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534384</v>
+        <v>534978</v>
       </c>
       <c r="R22" t="n">
-        <v>7265135</v>
+        <v>7265116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2901,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648466</v>
+        <v>122648475</v>
       </c>
       <c r="B23" t="n">
-        <v>74766</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534360</v>
+        <v>534909</v>
       </c>
       <c r="R23" t="n">
-        <v>7265163</v>
+        <v>7265136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,6 +2984,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2996,7 +3006,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3007,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648475</v>
+        <v>122648417</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
+        <v>91231</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3033,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534909</v>
+        <v>535039</v>
       </c>
       <c r="R24" t="n">
-        <v>7265136</v>
+        <v>7265098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,11 +3093,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648426</v>
+        <v>122648468</v>
       </c>
       <c r="B25" t="n">
-        <v>77607</v>
+        <v>90954</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534205</v>
+        <v>535007</v>
       </c>
       <c r="R25" t="n">
-        <v>7265119</v>
+        <v>7265120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3218,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3224,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648468</v>
+        <v>122648479</v>
       </c>
       <c r="B26" t="n">
-        <v>90851</v>
+        <v>91878</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3241,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535007</v>
+        <v>534384</v>
       </c>
       <c r="R26" t="n">
-        <v>7265120</v>
+        <v>7265135</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648418</v>
+        <v>122648403</v>
       </c>
       <c r="B27" t="n">
-        <v>92151</v>
+        <v>74847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534203</v>
+        <v>534162</v>
       </c>
       <c r="R27" t="n">
-        <v>7265101</v>
+        <v>7265113</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648396</v>
+        <v>122648355</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>90958</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534129</v>
+        <v>535896</v>
       </c>
       <c r="R28" t="n">
-        <v>7265112</v>
+        <v>7264601</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,11 +3519,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648427</v>
+        <v>122648461</v>
       </c>
       <c r="B29" t="n">
-        <v>74761</v>
+        <v>90958</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534208</v>
+        <v>534980</v>
       </c>
       <c r="R29" t="n">
         <v>7265114</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648464</v>
+        <v>122648436</v>
       </c>
       <c r="B30" t="n">
-        <v>79776</v>
+        <v>79872</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534978</v>
+        <v>535358</v>
       </c>
       <c r="R30" t="n">
-        <v>7265116</v>
+        <v>7264941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648478</v>
+        <v>122648390</v>
       </c>
       <c r="B31" t="n">
-        <v>90855</v>
+        <v>90954</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534371</v>
+        <v>535573</v>
       </c>
       <c r="R31" t="n">
-        <v>7265136</v>
+        <v>7264817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648324</v>
+        <v>122648398</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>8430</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535921</v>
+        <v>535550</v>
       </c>
       <c r="R32" t="n">
-        <v>7264587</v>
+        <v>7264828</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648466</v>
+        <v>122648465</v>
       </c>
       <c r="B2" t="n">
-        <v>74868</v>
+        <v>74675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534360</v>
+        <v>534361</v>
       </c>
       <c r="R2" t="n">
-        <v>7265163</v>
+        <v>7265171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648467</v>
+        <v>122648464</v>
       </c>
       <c r="B3" t="n">
-        <v>90936</v>
+        <v>79882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534384</v>
+        <v>534978</v>
       </c>
       <c r="R3" t="n">
-        <v>7265120</v>
+        <v>7265116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648462</v>
+        <v>122648479</v>
       </c>
       <c r="B4" t="n">
-        <v>91878</v>
+        <v>91882</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534952</v>
+        <v>534384</v>
       </c>
       <c r="R4" t="n">
-        <v>7265120</v>
+        <v>7265135</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648427</v>
+        <v>122648470</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>74868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534208</v>
+        <v>534374</v>
       </c>
       <c r="R5" t="n">
-        <v>7265114</v>
+        <v>7265137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648478</v>
+        <v>122648461</v>
       </c>
       <c r="B6" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534371</v>
+        <v>534980</v>
       </c>
       <c r="R6" t="n">
-        <v>7265136</v>
+        <v>7265114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648470</v>
+        <v>122648427</v>
       </c>
       <c r="B7" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534374</v>
+        <v>534208</v>
       </c>
       <c r="R7" t="n">
-        <v>7265137</v>
+        <v>7265114</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648396</v>
+        <v>122648418</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>92258</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534129</v>
+        <v>534203</v>
       </c>
       <c r="R8" t="n">
-        <v>7265112</v>
+        <v>7265101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1420,7 @@
         <v>122648324</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648474</v>
+        <v>122648396</v>
       </c>
       <c r="B10" t="n">
-        <v>82549</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534908</v>
+        <v>534129</v>
       </c>
       <c r="R10" t="n">
-        <v>7265138</v>
+        <v>7265112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,6 +1601,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648492</v>
+        <v>122648447</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534466</v>
+        <v>535157</v>
       </c>
       <c r="R11" t="n">
-        <v>7265134</v>
+        <v>7265060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648465</v>
+        <v>122648478</v>
       </c>
       <c r="B12" t="n">
-        <v>74675</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534361</v>
+        <v>534371</v>
       </c>
       <c r="R12" t="n">
-        <v>7265171</v>
+        <v>7265136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648426</v>
+        <v>122648399</v>
       </c>
       <c r="B13" t="n">
-        <v>77709</v>
+        <v>74855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534205</v>
+        <v>535550</v>
       </c>
       <c r="R13" t="n">
-        <v>7265119</v>
+        <v>7264829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648455</v>
+        <v>122648467</v>
       </c>
       <c r="B14" t="n">
-        <v>91385</v>
+        <v>90940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535016</v>
+        <v>534384</v>
       </c>
       <c r="R14" t="n">
-        <v>7265112</v>
+        <v>7265120</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648453</v>
+        <v>122648462</v>
       </c>
       <c r="B15" t="n">
-        <v>91385</v>
+        <v>91882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535037</v>
+        <v>534952</v>
       </c>
       <c r="R15" t="n">
-        <v>7265096</v>
+        <v>7265120</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648447</v>
+        <v>122648468</v>
       </c>
       <c r="B16" t="n">
-        <v>90936</v>
+        <v>90958</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535157</v>
+        <v>535007</v>
       </c>
       <c r="R16" t="n">
-        <v>7265060</v>
+        <v>7265120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648483</v>
+        <v>122648390</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>90958</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534458</v>
+        <v>535573</v>
       </c>
       <c r="R17" t="n">
-        <v>7265138</v>
+        <v>7264817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648399</v>
+        <v>122648466</v>
       </c>
       <c r="B18" t="n">
-        <v>74855</v>
+        <v>74868</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535550</v>
+        <v>534360</v>
       </c>
       <c r="R18" t="n">
-        <v>7264829</v>
+        <v>7265163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648428</v>
+        <v>122648474</v>
       </c>
       <c r="B19" t="n">
-        <v>90936</v>
+        <v>82553</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534215</v>
+        <v>534908</v>
       </c>
       <c r="R19" t="n">
-        <v>7265115</v>
+        <v>7265138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648456</v>
+        <v>122648426</v>
       </c>
       <c r="B20" t="n">
-        <v>91231</v>
+        <v>77709</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535016</v>
+        <v>534205</v>
       </c>
       <c r="R20" t="n">
-        <v>7265101</v>
+        <v>7265119</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648418</v>
+        <v>122648483</v>
       </c>
       <c r="B21" t="n">
-        <v>92254</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534203</v>
+        <v>534458</v>
       </c>
       <c r="R21" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648464</v>
+        <v>122648436</v>
       </c>
       <c r="B22" t="n">
-        <v>79878</v>
+        <v>79876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534978</v>
+        <v>535358</v>
       </c>
       <c r="R22" t="n">
-        <v>7265116</v>
+        <v>7264941</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648475</v>
+        <v>122648398</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>8430</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534909</v>
+        <v>535550</v>
       </c>
       <c r="R23" t="n">
-        <v>7265136</v>
+        <v>7264828</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,11 +2984,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3017,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648417</v>
+        <v>122648455</v>
       </c>
       <c r="B24" t="n">
-        <v>91231</v>
+        <v>91389</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535039</v>
+        <v>535016</v>
       </c>
       <c r="R24" t="n">
-        <v>7265098</v>
+        <v>7265112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3123,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648468</v>
+        <v>122648403</v>
       </c>
       <c r="B25" t="n">
-        <v>90954</v>
+        <v>74847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535007</v>
+        <v>534162</v>
       </c>
       <c r="R25" t="n">
-        <v>7265120</v>
+        <v>7265113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3229,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648479</v>
+        <v>122648428</v>
       </c>
       <c r="B26" t="n">
-        <v>91878</v>
+        <v>90940</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534384</v>
+        <v>534215</v>
       </c>
       <c r="R26" t="n">
-        <v>7265135</v>
+        <v>7265115</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3319,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648403</v>
+        <v>122648355</v>
       </c>
       <c r="B27" t="n">
-        <v>74847</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534162</v>
+        <v>535896</v>
       </c>
       <c r="R27" t="n">
-        <v>7265113</v>
+        <v>7264601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3425,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3441,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648355</v>
+        <v>122648456</v>
       </c>
       <c r="B28" t="n">
-        <v>90958</v>
+        <v>91235</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,21 +3452,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535896</v>
+        <v>535016</v>
       </c>
       <c r="R28" t="n">
-        <v>7264601</v>
+        <v>7265101</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648461</v>
+        <v>122648453</v>
       </c>
       <c r="B29" t="n">
-        <v>90958</v>
+        <v>91389</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,25 +3554,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534980</v>
+        <v>535037</v>
       </c>
       <c r="R29" t="n">
-        <v>7265114</v>
+        <v>7265096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648436</v>
+        <v>122648475</v>
       </c>
       <c r="B30" t="n">
-        <v>79872</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3660,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535358</v>
+        <v>534909</v>
       </c>
       <c r="R30" t="n">
-        <v>7264941</v>
+        <v>7265136</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,6 +3726,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648390</v>
+        <v>122648417</v>
       </c>
       <c r="B31" t="n">
-        <v>90954</v>
+        <v>91235</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535573</v>
+        <v>535039</v>
       </c>
       <c r="R31" t="n">
-        <v>7264817</v>
+        <v>7265098</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648398</v>
+        <v>122648492</v>
       </c>
       <c r="B32" t="n">
-        <v>8430</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535550</v>
+        <v>534466</v>
       </c>
       <c r="R32" t="n">
-        <v>7264828</v>
+        <v>7265134</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -3648,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648475</v>
+        <v>122648417</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534909</v>
+        <v>535039</v>
       </c>
       <c r="R30" t="n">
-        <v>7265136</v>
+        <v>7265098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3724,11 +3724,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3759,10 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648417</v>
+        <v>122648475</v>
       </c>
       <c r="B31" t="n">
-        <v>91235</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3770,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535039</v>
+        <v>534909</v>
       </c>
       <c r="R31" t="n">
-        <v>7265098</v>
+        <v>7265136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3835,6 +3830,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648465</v>
+        <v>122648455</v>
       </c>
       <c r="B2" t="n">
-        <v>74675</v>
+        <v>91389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534361</v>
+        <v>535016</v>
       </c>
       <c r="R2" t="n">
-        <v>7265171</v>
+        <v>7265112</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648464</v>
+        <v>122648456</v>
       </c>
       <c r="B3" t="n">
-        <v>79882</v>
+        <v>91235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534978</v>
+        <v>535016</v>
       </c>
       <c r="R3" t="n">
-        <v>7265116</v>
+        <v>7265101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648479</v>
+        <v>122648470</v>
       </c>
       <c r="B4" t="n">
-        <v>91882</v>
+        <v>74868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>534374</v>
       </c>
       <c r="R4" t="n">
-        <v>7265135</v>
+        <v>7265137</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648470</v>
+        <v>122648478</v>
       </c>
       <c r="B5" t="n">
-        <v>74868</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534374</v>
+        <v>534371</v>
       </c>
       <c r="R5" t="n">
-        <v>7265137</v>
+        <v>7265136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648461</v>
+        <v>122648466</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>74868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534980</v>
+        <v>534360</v>
       </c>
       <c r="R6" t="n">
-        <v>7265114</v>
+        <v>7265163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648427</v>
+        <v>122648467</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534208</v>
+        <v>534384</v>
       </c>
       <c r="R7" t="n">
-        <v>7265114</v>
+        <v>7265120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648418</v>
+        <v>122648492</v>
       </c>
       <c r="B8" t="n">
-        <v>92258</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534203</v>
+        <v>534466</v>
       </c>
       <c r="R8" t="n">
-        <v>7265101</v>
+        <v>7265134</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648324</v>
+        <v>122648461</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535921</v>
+        <v>534980</v>
       </c>
       <c r="R9" t="n">
-        <v>7264587</v>
+        <v>7265114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648396</v>
+        <v>122648417</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534129</v>
+        <v>535039</v>
       </c>
       <c r="R10" t="n">
-        <v>7265112</v>
+        <v>7265098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,11 +1601,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648447</v>
+        <v>122648355</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535157</v>
+        <v>535896</v>
       </c>
       <c r="R11" t="n">
-        <v>7265060</v>
+        <v>7264601</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648478</v>
+        <v>122648468</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90958</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534371</v>
+        <v>535007</v>
       </c>
       <c r="R12" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648399</v>
+        <v>122648462</v>
       </c>
       <c r="B13" t="n">
-        <v>74855</v>
+        <v>91882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535550</v>
+        <v>534952</v>
       </c>
       <c r="R13" t="n">
-        <v>7264829</v>
+        <v>7265120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648467</v>
+        <v>122648427</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534384</v>
+        <v>534208</v>
       </c>
       <c r="R14" t="n">
-        <v>7265120</v>
+        <v>7265114</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648462</v>
+        <v>122648324</v>
       </c>
       <c r="B15" t="n">
-        <v>91882</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534952</v>
+        <v>535921</v>
       </c>
       <c r="R15" t="n">
-        <v>7265120</v>
+        <v>7264587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648468</v>
+        <v>122648453</v>
       </c>
       <c r="B16" t="n">
-        <v>90958</v>
+        <v>91389</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535007</v>
+        <v>535037</v>
       </c>
       <c r="R16" t="n">
-        <v>7265120</v>
+        <v>7265096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648390</v>
+        <v>122648483</v>
       </c>
       <c r="B17" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535573</v>
+        <v>534458</v>
       </c>
       <c r="R17" t="n">
-        <v>7264817</v>
+        <v>7265138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648466</v>
+        <v>122648398</v>
       </c>
       <c r="B18" t="n">
-        <v>74868</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534360</v>
+        <v>535550</v>
       </c>
       <c r="R18" t="n">
-        <v>7265163</v>
+        <v>7264828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648426</v>
+        <v>122648447</v>
       </c>
       <c r="B20" t="n">
-        <v>77709</v>
+        <v>90940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534205</v>
+        <v>535157</v>
       </c>
       <c r="R20" t="n">
-        <v>7265119</v>
+        <v>7265060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2694,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648483</v>
+        <v>122648436</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534458</v>
+        <v>535358</v>
       </c>
       <c r="R21" t="n">
-        <v>7265138</v>
+        <v>7264941</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2800,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648436</v>
+        <v>122648428</v>
       </c>
       <c r="B22" t="n">
-        <v>79876</v>
+        <v>90940</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535358</v>
+        <v>534215</v>
       </c>
       <c r="R22" t="n">
-        <v>7264941</v>
+        <v>7265115</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648398</v>
+        <v>122648465</v>
       </c>
       <c r="B23" t="n">
-        <v>8430</v>
+        <v>74675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535550</v>
+        <v>534361</v>
       </c>
       <c r="R23" t="n">
-        <v>7264828</v>
+        <v>7265171</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2996,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3012,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648455</v>
+        <v>122648399</v>
       </c>
       <c r="B24" t="n">
-        <v>91389</v>
+        <v>74855</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535016</v>
+        <v>535550</v>
       </c>
       <c r="R24" t="n">
-        <v>7265112</v>
+        <v>7264829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648403</v>
+        <v>122648464</v>
       </c>
       <c r="B25" t="n">
-        <v>74847</v>
+        <v>79882</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534162</v>
+        <v>534978</v>
       </c>
       <c r="R25" t="n">
-        <v>7265113</v>
+        <v>7265116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3208,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3224,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648428</v>
+        <v>122648390</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3240,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534215</v>
+        <v>535573</v>
       </c>
       <c r="R26" t="n">
-        <v>7265115</v>
+        <v>7264817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3314,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648355</v>
+        <v>122648479</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>91882</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535896</v>
+        <v>534384</v>
       </c>
       <c r="R27" t="n">
-        <v>7264601</v>
+        <v>7265135</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648456</v>
+        <v>122648403</v>
       </c>
       <c r="B28" t="n">
-        <v>91235</v>
+        <v>74847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535016</v>
+        <v>534162</v>
       </c>
       <c r="R28" t="n">
-        <v>7265101</v>
+        <v>7265113</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3526,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3542,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648453</v>
+        <v>122648418</v>
       </c>
       <c r="B29" t="n">
-        <v>91389</v>
+        <v>92258</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535037</v>
+        <v>534203</v>
       </c>
       <c r="R29" t="n">
-        <v>7265096</v>
+        <v>7265101</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,7 +3632,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3648,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648417</v>
+        <v>122648396</v>
       </c>
       <c r="B30" t="n">
-        <v>91235</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3664,21 +3659,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3688,10 +3683,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535039</v>
+        <v>534129</v>
       </c>
       <c r="R30" t="n">
-        <v>7265098</v>
+        <v>7265112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,6 +3721,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3754,10 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648475</v>
+        <v>122648426</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534909</v>
+        <v>534205</v>
       </c>
       <c r="R31" t="n">
-        <v>7265136</v>
+        <v>7265119</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,11 +3832,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3854,7 +3849,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648492</v>
+        <v>122648475</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534466</v>
+        <v>534909</v>
       </c>
       <c r="R32" t="n">
-        <v>7265134</v>
+        <v>7265136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,6 +3938,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648455</v>
+        <v>122648468</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535016</v>
+        <v>535007</v>
       </c>
       <c r="R2" t="n">
-        <v>7265112</v>
+        <v>7265120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648456</v>
+        <v>122648467</v>
       </c>
       <c r="B3" t="n">
-        <v>91235</v>
+        <v>90940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535016</v>
+        <v>534384</v>
       </c>
       <c r="R3" t="n">
-        <v>7265101</v>
+        <v>7265120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648470</v>
+        <v>122648462</v>
       </c>
       <c r="B4" t="n">
-        <v>74868</v>
+        <v>91882</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534374</v>
+        <v>534952</v>
       </c>
       <c r="R4" t="n">
-        <v>7265137</v>
+        <v>7265120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648478</v>
+        <v>122648428</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534371</v>
+        <v>534215</v>
       </c>
       <c r="R5" t="n">
-        <v>7265136</v>
+        <v>7265115</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648467</v>
+        <v>122648492</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534384</v>
+        <v>534466</v>
       </c>
       <c r="R7" t="n">
-        <v>7265120</v>
+        <v>7265134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648492</v>
+        <v>122648475</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534466</v>
+        <v>534909</v>
       </c>
       <c r="R8" t="n">
-        <v>7265134</v>
+        <v>7265136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,6 +1389,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648461</v>
+        <v>122648426</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>77709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534980</v>
+        <v>534205</v>
       </c>
       <c r="R9" t="n">
-        <v>7265114</v>
+        <v>7265119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1517,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648417</v>
+        <v>122648355</v>
       </c>
       <c r="B10" t="n">
-        <v>91235</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535039</v>
+        <v>535896</v>
       </c>
       <c r="R10" t="n">
-        <v>7265098</v>
+        <v>7264601</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648355</v>
+        <v>122648461</v>
       </c>
       <c r="B11" t="n">
         <v>90962</v>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535896</v>
+        <v>534980</v>
       </c>
       <c r="R11" t="n">
-        <v>7264601</v>
+        <v>7265114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648468</v>
+        <v>122648464</v>
       </c>
       <c r="B12" t="n">
-        <v>90958</v>
+        <v>79882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535007</v>
+        <v>534978</v>
       </c>
       <c r="R12" t="n">
-        <v>7265120</v>
+        <v>7265116</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648462</v>
+        <v>122648474</v>
       </c>
       <c r="B13" t="n">
-        <v>91882</v>
+        <v>82553</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534952</v>
+        <v>534908</v>
       </c>
       <c r="R13" t="n">
-        <v>7265120</v>
+        <v>7265138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648427</v>
+        <v>122648418</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>92258</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534208</v>
+        <v>534203</v>
       </c>
       <c r="R14" t="n">
-        <v>7265114</v>
+        <v>7265101</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648324</v>
+        <v>122648396</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535921</v>
+        <v>534129</v>
       </c>
       <c r="R15" t="n">
-        <v>7264587</v>
+        <v>7265112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,6 +2136,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2148,7 +2158,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648453</v>
+        <v>122648455</v>
       </c>
       <c r="B16" t="n">
         <v>91389</v>
@@ -2199,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535037</v>
+        <v>535016</v>
       </c>
       <c r="R16" t="n">
-        <v>7265096</v>
+        <v>7265112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648483</v>
+        <v>122648479</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>91882</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534458</v>
+        <v>534384</v>
       </c>
       <c r="R17" t="n">
-        <v>7265138</v>
+        <v>7265135</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2370,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648398</v>
+        <v>122648417</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>91235</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535550</v>
+        <v>535039</v>
       </c>
       <c r="R18" t="n">
-        <v>7264828</v>
+        <v>7265098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2476,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648474</v>
+        <v>122648403</v>
       </c>
       <c r="B19" t="n">
-        <v>82553</v>
+        <v>74847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2499,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534908</v>
+        <v>534162</v>
       </c>
       <c r="R19" t="n">
-        <v>7265138</v>
+        <v>7265113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2582,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648447</v>
+        <v>122648456</v>
       </c>
       <c r="B20" t="n">
-        <v>90940</v>
+        <v>91235</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2609,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535157</v>
+        <v>535016</v>
       </c>
       <c r="R20" t="n">
-        <v>7265060</v>
+        <v>7265101</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648436</v>
+        <v>122648483</v>
       </c>
       <c r="B21" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535358</v>
+        <v>534458</v>
       </c>
       <c r="R21" t="n">
-        <v>7264941</v>
+        <v>7265138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2794,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648428</v>
+        <v>122648390</v>
       </c>
       <c r="B22" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534215</v>
+        <v>535573</v>
       </c>
       <c r="R22" t="n">
-        <v>7265115</v>
+        <v>7264817</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2900,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2901,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648465</v>
+        <v>122648324</v>
       </c>
       <c r="B23" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2923,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534361</v>
+        <v>535921</v>
       </c>
       <c r="R23" t="n">
-        <v>7265171</v>
+        <v>7264587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +3006,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3007,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648399</v>
+        <v>122648436</v>
       </c>
       <c r="B24" t="n">
-        <v>74855</v>
+        <v>79876</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3029,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535550</v>
+        <v>535358</v>
       </c>
       <c r="R24" t="n">
-        <v>7264829</v>
+        <v>7264941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648464</v>
+        <v>122648465</v>
       </c>
       <c r="B25" t="n">
-        <v>79882</v>
+        <v>74675</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534978</v>
+        <v>534361</v>
       </c>
       <c r="R25" t="n">
-        <v>7265116</v>
+        <v>7265171</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,7 +3218,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3219,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648390</v>
+        <v>122648447</v>
       </c>
       <c r="B26" t="n">
-        <v>90958</v>
+        <v>90940</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3245,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535573</v>
+        <v>535157</v>
       </c>
       <c r="R26" t="n">
-        <v>7264817</v>
+        <v>7265060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648479</v>
+        <v>122648399</v>
       </c>
       <c r="B27" t="n">
-        <v>91882</v>
+        <v>74855</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534384</v>
+        <v>535550</v>
       </c>
       <c r="R27" t="n">
-        <v>7265135</v>
+        <v>7264829</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3430,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3431,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648403</v>
+        <v>122648398</v>
       </c>
       <c r="B28" t="n">
-        <v>74847</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534162</v>
+        <v>535550</v>
       </c>
       <c r="R28" t="n">
-        <v>7265113</v>
+        <v>7264828</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3537,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648418</v>
+        <v>122648470</v>
       </c>
       <c r="B29" t="n">
-        <v>92258</v>
+        <v>74868</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3559,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534203</v>
+        <v>534374</v>
       </c>
       <c r="R29" t="n">
-        <v>7265101</v>
+        <v>7265137</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648396</v>
+        <v>122648427</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3683,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534129</v>
+        <v>534208</v>
       </c>
       <c r="R30" t="n">
-        <v>7265112</v>
+        <v>7265114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,11 +3729,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3754,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648426</v>
+        <v>122648478</v>
       </c>
       <c r="B31" t="n">
-        <v>77709</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3794,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534205</v>
+        <v>534371</v>
       </c>
       <c r="R31" t="n">
-        <v>7265119</v>
+        <v>7265136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648475</v>
+        <v>122648453</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>91389</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3872,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534909</v>
+        <v>535037</v>
       </c>
       <c r="R32" t="n">
-        <v>7265136</v>
+        <v>7265096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,11 +3943,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648455</v>
+        <v>122648417</v>
       </c>
       <c r="B16" t="n">
-        <v>91389</v>
+        <v>91235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535016</v>
+        <v>535039</v>
       </c>
       <c r="R16" t="n">
-        <v>7265112</v>
+        <v>7265098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648479</v>
+        <v>122648455</v>
       </c>
       <c r="B17" t="n">
-        <v>91882</v>
+        <v>91389</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R17" t="n">
-        <v>7265135</v>
+        <v>7265112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648417</v>
+        <v>122648479</v>
       </c>
       <c r="B18" t="n">
-        <v>91235</v>
+        <v>91882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2393,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535039</v>
+        <v>534384</v>
       </c>
       <c r="R18" t="n">
-        <v>7265098</v>
+        <v>7265135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648468</v>
+        <v>122648427</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535007</v>
+        <v>534208</v>
       </c>
       <c r="R2" t="n">
-        <v>7265120</v>
+        <v>7265114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648467</v>
+        <v>122648390</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534384</v>
+        <v>535573</v>
       </c>
       <c r="R3" t="n">
-        <v>7265120</v>
+        <v>7264817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648428</v>
+        <v>122648324</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534215</v>
+        <v>535921</v>
       </c>
       <c r="R5" t="n">
-        <v>7265115</v>
+        <v>7264587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648466</v>
+        <v>122648492</v>
       </c>
       <c r="B6" t="n">
-        <v>74868</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534360</v>
+        <v>534466</v>
       </c>
       <c r="R6" t="n">
-        <v>7265163</v>
+        <v>7265134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648492</v>
+        <v>122648417</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534466</v>
+        <v>535039</v>
       </c>
       <c r="R7" t="n">
-        <v>7265134</v>
+        <v>7265098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648475</v>
+        <v>122648428</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534909</v>
+        <v>534215</v>
       </c>
       <c r="R8" t="n">
-        <v>7265136</v>
+        <v>7265115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1389,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648426</v>
+        <v>122648474</v>
       </c>
       <c r="B9" t="n">
-        <v>77709</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534205</v>
+        <v>534908</v>
       </c>
       <c r="R9" t="n">
-        <v>7265119</v>
+        <v>7265138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648355</v>
+        <v>122648466</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>74868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535896</v>
+        <v>534360</v>
       </c>
       <c r="R10" t="n">
-        <v>7264601</v>
+        <v>7265163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648461</v>
+        <v>122648398</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534980</v>
+        <v>535550</v>
       </c>
       <c r="R11" t="n">
-        <v>7265114</v>
+        <v>7264828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648464</v>
+        <v>122648399</v>
       </c>
       <c r="B12" t="n">
-        <v>79882</v>
+        <v>74855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534978</v>
+        <v>535550</v>
       </c>
       <c r="R12" t="n">
-        <v>7265116</v>
+        <v>7264829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648474</v>
+        <v>122648436</v>
       </c>
       <c r="B13" t="n">
-        <v>82553</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534908</v>
+        <v>535358</v>
       </c>
       <c r="R13" t="n">
-        <v>7265138</v>
+        <v>7264941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648418</v>
+        <v>122648470</v>
       </c>
       <c r="B14" t="n">
-        <v>92258</v>
+        <v>74868</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534203</v>
+        <v>534374</v>
       </c>
       <c r="R14" t="n">
-        <v>7265101</v>
+        <v>7265137</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648396</v>
+        <v>122648479</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>91882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534129</v>
+        <v>534384</v>
       </c>
       <c r="R15" t="n">
-        <v>7265112</v>
+        <v>7265135</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,11 +2129,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648417</v>
+        <v>122648418</v>
       </c>
       <c r="B16" t="n">
-        <v>91235</v>
+        <v>92258</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535039</v>
+        <v>534203</v>
       </c>
       <c r="R16" t="n">
-        <v>7265098</v>
+        <v>7265101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2275,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648455</v>
+        <v>122648465</v>
       </c>
       <c r="B17" t="n">
-        <v>91389</v>
+        <v>74675</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6428</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535016</v>
+        <v>534361</v>
       </c>
       <c r="R17" t="n">
-        <v>7265112</v>
+        <v>7265171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2381,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648479</v>
+        <v>122648456</v>
       </c>
       <c r="B18" t="n">
-        <v>91882</v>
+        <v>91235</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R18" t="n">
-        <v>7265135</v>
+        <v>7265101</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2487,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648403</v>
+        <v>122648468</v>
       </c>
       <c r="B19" t="n">
-        <v>74847</v>
+        <v>90958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534162</v>
+        <v>535007</v>
       </c>
       <c r="R19" t="n">
-        <v>7265113</v>
+        <v>7265120</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2593,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648456</v>
+        <v>122648467</v>
       </c>
       <c r="B20" t="n">
-        <v>91235</v>
+        <v>90940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535016</v>
+        <v>534384</v>
       </c>
       <c r="R20" t="n">
-        <v>7265101</v>
+        <v>7265120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648483</v>
+        <v>122648355</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534458</v>
+        <v>535896</v>
       </c>
       <c r="R21" t="n">
-        <v>7265138</v>
+        <v>7264601</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648390</v>
+        <v>122648475</v>
       </c>
       <c r="B22" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535573</v>
+        <v>534909</v>
       </c>
       <c r="R22" t="n">
-        <v>7264817</v>
+        <v>7265136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2883,6 +2873,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2911,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648324</v>
+        <v>122648478</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,21 +2922,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535921</v>
+        <v>534371</v>
       </c>
       <c r="R23" t="n">
-        <v>7264587</v>
+        <v>7265136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3017,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648436</v>
+        <v>122648447</v>
       </c>
       <c r="B24" t="n">
-        <v>79876</v>
+        <v>90940</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535358</v>
+        <v>535157</v>
       </c>
       <c r="R24" t="n">
-        <v>7264941</v>
+        <v>7265060</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648465</v>
+        <v>122648403</v>
       </c>
       <c r="B25" t="n">
-        <v>74675</v>
+        <v>74847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,21 +3134,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534361</v>
+        <v>534162</v>
       </c>
       <c r="R25" t="n">
-        <v>7265171</v>
+        <v>7265113</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648447</v>
+        <v>122648455</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>91389</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535157</v>
+        <v>535016</v>
       </c>
       <c r="R26" t="n">
-        <v>7265060</v>
+        <v>7265112</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648399</v>
+        <v>122648461</v>
       </c>
       <c r="B27" t="n">
-        <v>74855</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535550</v>
+        <v>534980</v>
       </c>
       <c r="R27" t="n">
-        <v>7264829</v>
+        <v>7265114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648398</v>
+        <v>122648426</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>77709</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535550</v>
+        <v>534205</v>
       </c>
       <c r="R28" t="n">
-        <v>7264828</v>
+        <v>7265119</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3531,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648470</v>
+        <v>122648396</v>
       </c>
       <c r="B29" t="n">
-        <v>74868</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,21 +3558,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534374</v>
+        <v>534129</v>
       </c>
       <c r="R29" t="n">
-        <v>7265137</v>
+        <v>7265112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,6 +3618,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648427</v>
+        <v>122648464</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3665,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534208</v>
+        <v>534978</v>
       </c>
       <c r="R30" t="n">
-        <v>7265114</v>
+        <v>7265116</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648478</v>
+        <v>122648453</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>91389</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,25 +3771,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534371</v>
+        <v>535037</v>
       </c>
       <c r="R31" t="n">
-        <v>7265136</v>
+        <v>7265096</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648453</v>
+        <v>122648483</v>
       </c>
       <c r="B32" t="n">
-        <v>91389</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535037</v>
+        <v>534458</v>
       </c>
       <c r="R32" t="n">
-        <v>7265096</v>
+        <v>7265138</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648492</v>
+        <v>122648417</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>91235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534466</v>
+        <v>535039</v>
       </c>
       <c r="R6" t="n">
-        <v>7265134</v>
+        <v>7265098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648417</v>
+        <v>122648428</v>
       </c>
       <c r="B7" t="n">
-        <v>91235</v>
+        <v>90940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535039</v>
+        <v>534215</v>
       </c>
       <c r="R7" t="n">
-        <v>7265098</v>
+        <v>7265115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648428</v>
+        <v>122648492</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534215</v>
+        <v>534466</v>
       </c>
       <c r="R8" t="n">
-        <v>7265115</v>
+        <v>7265134</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648398</v>
+        <v>122648436</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>79876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535550</v>
+        <v>535358</v>
       </c>
       <c r="R11" t="n">
-        <v>7264828</v>
+        <v>7264941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648436</v>
+        <v>122648398</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>8430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535358</v>
+        <v>535550</v>
       </c>
       <c r="R13" t="n">
-        <v>7264941</v>
+        <v>7264828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648403</v>
+        <v>122648461</v>
       </c>
       <c r="B25" t="n">
-        <v>74847</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534162</v>
+        <v>534980</v>
       </c>
       <c r="R25" t="n">
-        <v>7265113</v>
+        <v>7265114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3224,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648455</v>
+        <v>122648403</v>
       </c>
       <c r="B26" t="n">
-        <v>91389</v>
+        <v>74847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535016</v>
+        <v>534162</v>
       </c>
       <c r="R26" t="n">
-        <v>7265112</v>
+        <v>7265113</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648461</v>
+        <v>122648455</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>91389</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534980</v>
+        <v>535016</v>
       </c>
       <c r="R27" t="n">
-        <v>7265114</v>
+        <v>7265112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648417</v>
+        <v>122648492</v>
       </c>
       <c r="B6" t="n">
-        <v>91235</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535039</v>
+        <v>534466</v>
       </c>
       <c r="R6" t="n">
-        <v>7265098</v>
+        <v>7265134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648428</v>
+        <v>122648417</v>
       </c>
       <c r="B7" t="n">
-        <v>90940</v>
+        <v>91235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534215</v>
+        <v>535039</v>
       </c>
       <c r="R7" t="n">
-        <v>7265115</v>
+        <v>7265098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648492</v>
+        <v>122648428</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>90940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534466</v>
+        <v>534215</v>
       </c>
       <c r="R8" t="n">
-        <v>7265134</v>
+        <v>7265115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648436</v>
+        <v>122648398</v>
       </c>
       <c r="B11" t="n">
-        <v>79876</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535358</v>
+        <v>535550</v>
       </c>
       <c r="R11" t="n">
-        <v>7264941</v>
+        <v>7264828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648398</v>
+        <v>122648436</v>
       </c>
       <c r="B13" t="n">
-        <v>8430</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535550</v>
+        <v>535358</v>
       </c>
       <c r="R13" t="n">
-        <v>7264828</v>
+        <v>7264941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648427</v>
+        <v>122648465</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534208</v>
+        <v>534361</v>
       </c>
       <c r="R2" t="n">
-        <v>7265114</v>
+        <v>7265171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648390</v>
+        <v>122648478</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535573</v>
+        <v>534371</v>
       </c>
       <c r="R3" t="n">
-        <v>7264817</v>
+        <v>7265136</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648462</v>
+        <v>122648428</v>
       </c>
       <c r="B4" t="n">
-        <v>91882</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534952</v>
+        <v>534215</v>
       </c>
       <c r="R4" t="n">
-        <v>7265120</v>
+        <v>7265115</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648324</v>
+        <v>122648468</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535921</v>
+        <v>535007</v>
       </c>
       <c r="R5" t="n">
-        <v>7264587</v>
+        <v>7265120</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648492</v>
+        <v>122648467</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534466</v>
+        <v>534384</v>
       </c>
       <c r="R6" t="n">
-        <v>7265134</v>
+        <v>7265120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648417</v>
+        <v>122648399</v>
       </c>
       <c r="B7" t="n">
-        <v>91235</v>
+        <v>74855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535039</v>
+        <v>535550</v>
       </c>
       <c r="R7" t="n">
-        <v>7265098</v>
+        <v>7264829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648428</v>
+        <v>122648324</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534215</v>
+        <v>535921</v>
       </c>
       <c r="R8" t="n">
-        <v>7265115</v>
+        <v>7264587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648474</v>
+        <v>122648417</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>91243</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534908</v>
+        <v>535039</v>
       </c>
       <c r="R9" t="n">
-        <v>7265138</v>
+        <v>7265098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648466</v>
+        <v>122648436</v>
       </c>
       <c r="B10" t="n">
-        <v>74868</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534360</v>
+        <v>535358</v>
       </c>
       <c r="R10" t="n">
-        <v>7265163</v>
+        <v>7264941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648398</v>
+        <v>122648462</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
+        <v>91890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535550</v>
+        <v>534952</v>
       </c>
       <c r="R11" t="n">
-        <v>7264828</v>
+        <v>7265120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648399</v>
+        <v>122648492</v>
       </c>
       <c r="B12" t="n">
-        <v>74855</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535550</v>
+        <v>534466</v>
       </c>
       <c r="R12" t="n">
-        <v>7264829</v>
+        <v>7265134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648436</v>
+        <v>122648426</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>77709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535358</v>
+        <v>534205</v>
       </c>
       <c r="R13" t="n">
-        <v>7264941</v>
+        <v>7265119</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648470</v>
+        <v>122648455</v>
       </c>
       <c r="B14" t="n">
-        <v>74868</v>
+        <v>91397</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534374</v>
+        <v>535016</v>
       </c>
       <c r="R14" t="n">
-        <v>7265137</v>
+        <v>7265112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648479</v>
+        <v>122648474</v>
       </c>
       <c r="B15" t="n">
-        <v>91882</v>
+        <v>82553</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534384</v>
+        <v>534908</v>
       </c>
       <c r="R15" t="n">
-        <v>7265135</v>
+        <v>7265138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648418</v>
+        <v>122648453</v>
       </c>
       <c r="B16" t="n">
-        <v>92258</v>
+        <v>91397</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534203</v>
+        <v>535037</v>
       </c>
       <c r="R16" t="n">
-        <v>7265101</v>
+        <v>7265096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648465</v>
+        <v>122648418</v>
       </c>
       <c r="B17" t="n">
-        <v>74675</v>
+        <v>92266</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6428</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534361</v>
+        <v>534203</v>
       </c>
       <c r="R17" t="n">
-        <v>7265171</v>
+        <v>7265101</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648456</v>
+        <v>122648466</v>
       </c>
       <c r="B18" t="n">
-        <v>91235</v>
+        <v>74868</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535016</v>
+        <v>534360</v>
       </c>
       <c r="R18" t="n">
-        <v>7265101</v>
+        <v>7265163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648468</v>
+        <v>122648398</v>
       </c>
       <c r="B19" t="n">
-        <v>90958</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535007</v>
+        <v>535550</v>
       </c>
       <c r="R19" t="n">
-        <v>7265120</v>
+        <v>7264828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648467</v>
+        <v>122648447</v>
       </c>
       <c r="B20" t="n">
-        <v>90940</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534384</v>
+        <v>535157</v>
       </c>
       <c r="R20" t="n">
-        <v>7265120</v>
+        <v>7265060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648355</v>
+        <v>122648470</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>74868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535896</v>
+        <v>534374</v>
       </c>
       <c r="R21" t="n">
-        <v>7264601</v>
+        <v>7265137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648475</v>
+        <v>122648355</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534909</v>
+        <v>535896</v>
       </c>
       <c r="R22" t="n">
-        <v>7265136</v>
+        <v>7264601</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,11 +2873,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2895,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2906,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648478</v>
+        <v>122648390</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>90966</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534371</v>
+        <v>535573</v>
       </c>
       <c r="R23" t="n">
-        <v>7265136</v>
+        <v>7264817</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2996,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3012,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648447</v>
+        <v>122648464</v>
       </c>
       <c r="B24" t="n">
-        <v>90940</v>
+        <v>79882</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535157</v>
+        <v>534978</v>
       </c>
       <c r="R24" t="n">
-        <v>7265060</v>
+        <v>7265116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648461</v>
+        <v>122648456</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>91243</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534980</v>
+        <v>535016</v>
       </c>
       <c r="R25" t="n">
-        <v>7265114</v>
+        <v>7265101</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648403</v>
+        <v>122648479</v>
       </c>
       <c r="B26" t="n">
-        <v>74847</v>
+        <v>91890</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3240,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534162</v>
+        <v>534384</v>
       </c>
       <c r="R26" t="n">
-        <v>7265113</v>
+        <v>7265135</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648455</v>
+        <v>122648427</v>
       </c>
       <c r="B27" t="n">
-        <v>91389</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535016</v>
+        <v>534208</v>
       </c>
       <c r="R27" t="n">
-        <v>7265112</v>
+        <v>7265114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648426</v>
+        <v>122648461</v>
       </c>
       <c r="B28" t="n">
-        <v>77709</v>
+        <v>90970</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,21 +3447,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534205</v>
+        <v>534980</v>
       </c>
       <c r="R28" t="n">
-        <v>7265119</v>
+        <v>7265114</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3526,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3542,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648396</v>
+        <v>122648403</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534129</v>
+        <v>534162</v>
       </c>
       <c r="R29" t="n">
-        <v>7265112</v>
+        <v>7265113</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,11 +3613,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648464</v>
+        <v>122648396</v>
       </c>
       <c r="B30" t="n">
-        <v>79882</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3655,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3683,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534978</v>
+        <v>534129</v>
       </c>
       <c r="R30" t="n">
-        <v>7265116</v>
+        <v>7265112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,6 +3721,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3748,7 +3743,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648453</v>
+        <v>122648475</v>
       </c>
       <c r="B31" t="n">
-        <v>91389</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,25 +3766,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3794,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535037</v>
+        <v>534909</v>
       </c>
       <c r="R31" t="n">
-        <v>7265096</v>
+        <v>7265136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,6 +3832,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648390</v>
+        <v>122648464</v>
       </c>
       <c r="B23" t="n">
-        <v>90966</v>
+        <v>79882</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535573</v>
+        <v>534978</v>
       </c>
       <c r="R23" t="n">
-        <v>7264817</v>
+        <v>7265116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648464</v>
+        <v>122648390</v>
       </c>
       <c r="B24" t="n">
-        <v>79882</v>
+        <v>90966</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534978</v>
+        <v>535573</v>
       </c>
       <c r="R24" t="n">
-        <v>7265116</v>
+        <v>7264817</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648465</v>
+        <v>122648478</v>
       </c>
       <c r="B2" t="n">
-        <v>74675</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534361</v>
+        <v>534371</v>
       </c>
       <c r="R2" t="n">
-        <v>7265171</v>
+        <v>7265136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648478</v>
+        <v>122648428</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534371</v>
+        <v>534215</v>
       </c>
       <c r="R3" t="n">
-        <v>7265136</v>
+        <v>7265115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648428</v>
+        <v>122648467</v>
       </c>
       <c r="B4" t="n">
         <v>90948</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534215</v>
+        <v>534384</v>
       </c>
       <c r="R4" t="n">
-        <v>7265115</v>
+        <v>7265120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648468</v>
+        <v>122648483</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535007</v>
+        <v>534458</v>
       </c>
       <c r="R5" t="n">
-        <v>7265120</v>
+        <v>7265138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648467</v>
+        <v>122648403</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>74847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534384</v>
+        <v>534162</v>
       </c>
       <c r="R6" t="n">
-        <v>7265120</v>
+        <v>7265113</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648399</v>
+        <v>122648436</v>
       </c>
       <c r="B7" t="n">
-        <v>74855</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535550</v>
+        <v>535358</v>
       </c>
       <c r="R7" t="n">
-        <v>7264829</v>
+        <v>7264941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648324</v>
+        <v>122648468</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535921</v>
+        <v>535007</v>
       </c>
       <c r="R8" t="n">
-        <v>7264587</v>
+        <v>7265120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648417</v>
+        <v>122648355</v>
       </c>
       <c r="B9" t="n">
-        <v>91243</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535039</v>
+        <v>535896</v>
       </c>
       <c r="R9" t="n">
-        <v>7265098</v>
+        <v>7264601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648436</v>
+        <v>122648390</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>90966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535358</v>
+        <v>535573</v>
       </c>
       <c r="R10" t="n">
-        <v>7264941</v>
+        <v>7264817</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648462</v>
+        <v>122648464</v>
       </c>
       <c r="B11" t="n">
-        <v>91890</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534952</v>
+        <v>534978</v>
       </c>
       <c r="R11" t="n">
-        <v>7265120</v>
+        <v>7265116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648492</v>
+        <v>122648461</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534466</v>
+        <v>534980</v>
       </c>
       <c r="R12" t="n">
-        <v>7265134</v>
+        <v>7265114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648426</v>
+        <v>122648417</v>
       </c>
       <c r="B13" t="n">
-        <v>77709</v>
+        <v>91243</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534205</v>
+        <v>535039</v>
       </c>
       <c r="R13" t="n">
-        <v>7265119</v>
+        <v>7265098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648455</v>
+        <v>122648492</v>
       </c>
       <c r="B14" t="n">
-        <v>91397</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535016</v>
+        <v>534466</v>
       </c>
       <c r="R14" t="n">
-        <v>7265112</v>
+        <v>7265134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648474</v>
+        <v>122648455</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>91397</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534908</v>
+        <v>535016</v>
       </c>
       <c r="R15" t="n">
-        <v>7265138</v>
+        <v>7265112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648453</v>
+        <v>122648426</v>
       </c>
       <c r="B16" t="n">
-        <v>91397</v>
+        <v>77709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535037</v>
+        <v>534205</v>
       </c>
       <c r="R16" t="n">
-        <v>7265096</v>
+        <v>7265119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648418</v>
+        <v>122648456</v>
       </c>
       <c r="B17" t="n">
-        <v>92266</v>
+        <v>91243</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534203</v>
+        <v>535016</v>
       </c>
       <c r="R17" t="n">
         <v>7265101</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648466</v>
+        <v>122648453</v>
       </c>
       <c r="B18" t="n">
-        <v>74868</v>
+        <v>91397</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534360</v>
+        <v>535037</v>
       </c>
       <c r="R18" t="n">
-        <v>7265163</v>
+        <v>7265096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648398</v>
+        <v>122648324</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535550</v>
+        <v>535921</v>
       </c>
       <c r="R19" t="n">
-        <v>7264828</v>
+        <v>7264587</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648447</v>
+        <v>122648466</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>74868</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535157</v>
+        <v>534360</v>
       </c>
       <c r="R20" t="n">
-        <v>7265060</v>
+        <v>7265163</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648470</v>
+        <v>122648462</v>
       </c>
       <c r="B21" t="n">
-        <v>74868</v>
+        <v>91890</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534374</v>
+        <v>534952</v>
       </c>
       <c r="R21" t="n">
-        <v>7265137</v>
+        <v>7265120</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648355</v>
+        <v>122648479</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>91890</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535896</v>
+        <v>534384</v>
       </c>
       <c r="R22" t="n">
-        <v>7264601</v>
+        <v>7265135</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648464</v>
+        <v>122648398</v>
       </c>
       <c r="B23" t="n">
-        <v>79882</v>
+        <v>8430</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534978</v>
+        <v>535550</v>
       </c>
       <c r="R23" t="n">
-        <v>7265116</v>
+        <v>7264828</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648390</v>
+        <v>122648399</v>
       </c>
       <c r="B24" t="n">
-        <v>90966</v>
+        <v>74855</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535573</v>
+        <v>535550</v>
       </c>
       <c r="R24" t="n">
-        <v>7264817</v>
+        <v>7264829</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648456</v>
+        <v>122648396</v>
       </c>
       <c r="B25" t="n">
-        <v>91243</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535016</v>
+        <v>534129</v>
       </c>
       <c r="R25" t="n">
-        <v>7265101</v>
+        <v>7265112</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,6 +3191,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3208,7 +3213,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3219,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648479</v>
+        <v>122648418</v>
       </c>
       <c r="B26" t="n">
-        <v>91890</v>
+        <v>92266</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3240,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3259,10 +3264,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534384</v>
+        <v>534203</v>
       </c>
       <c r="R26" t="n">
-        <v>7265135</v>
+        <v>7265101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648427</v>
+        <v>122648465</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534208</v>
+        <v>534361</v>
       </c>
       <c r="R27" t="n">
-        <v>7265114</v>
+        <v>7265171</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648461</v>
+        <v>122648427</v>
       </c>
       <c r="B28" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3452,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,7 +3476,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534980</v>
+        <v>534208</v>
       </c>
       <c r="R28" t="n">
         <v>7265114</v>
@@ -3526,7 +3531,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3537,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648403</v>
+        <v>122648475</v>
       </c>
       <c r="B29" t="n">
-        <v>74847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3554,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3577,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534162</v>
+        <v>534909</v>
       </c>
       <c r="R29" t="n">
-        <v>7265113</v>
+        <v>7265136</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,6 +3620,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3632,7 +3642,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3643,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648396</v>
+        <v>122648447</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3683,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534129</v>
+        <v>535157</v>
       </c>
       <c r="R30" t="n">
-        <v>7265112</v>
+        <v>7265060</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,11 +3731,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3743,7 +3748,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3754,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648475</v>
+        <v>122648474</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3794,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534909</v>
+        <v>534908</v>
       </c>
       <c r="R31" t="n">
-        <v>7265136</v>
+        <v>7265138</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,11 +3835,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648483</v>
+        <v>122648470</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534458</v>
+        <v>534374</v>
       </c>
       <c r="R32" t="n">
-        <v>7265138</v>
+        <v>7265137</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648468</v>
+        <v>122648355</v>
       </c>
       <c r="B8" t="n">
-        <v>90966</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535007</v>
+        <v>535896</v>
       </c>
       <c r="R8" t="n">
-        <v>7265120</v>
+        <v>7264601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648355</v>
+        <v>122648468</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>90966</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535896</v>
+        <v>535007</v>
       </c>
       <c r="R9" t="n">
-        <v>7264601</v>
+        <v>7265120</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648465</v>
+        <v>122648427</v>
       </c>
       <c r="B27" t="n">
-        <v>74675</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534361</v>
+        <v>534208</v>
       </c>
       <c r="R27" t="n">
-        <v>7265171</v>
+        <v>7265114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648427</v>
+        <v>122648465</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>74675</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534208</v>
+        <v>534361</v>
       </c>
       <c r="R28" t="n">
-        <v>7265114</v>
+        <v>7265171</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648355</v>
+        <v>122648468</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>90966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535896</v>
+        <v>535007</v>
       </c>
       <c r="R8" t="n">
-        <v>7264601</v>
+        <v>7265120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648468</v>
+        <v>122648355</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535007</v>
+        <v>535896</v>
       </c>
       <c r="R9" t="n">
-        <v>7265120</v>
+        <v>7264601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648478</v>
+        <v>122648467</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534371</v>
+        <v>534384</v>
       </c>
       <c r="R2" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648428</v>
+        <v>122648399</v>
       </c>
       <c r="B3" t="n">
-        <v>90948</v>
+        <v>74855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534215</v>
+        <v>535550</v>
       </c>
       <c r="R3" t="n">
-        <v>7265115</v>
+        <v>7264829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648467</v>
+        <v>122648436</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>535358</v>
       </c>
       <c r="R4" t="n">
-        <v>7265120</v>
+        <v>7264941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648483</v>
+        <v>122648492</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534458</v>
+        <v>534466</v>
       </c>
       <c r="R5" t="n">
-        <v>7265138</v>
+        <v>7265134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648403</v>
+        <v>122648417</v>
       </c>
       <c r="B6" t="n">
-        <v>74847</v>
+        <v>91243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534162</v>
+        <v>535039</v>
       </c>
       <c r="R6" t="n">
-        <v>7265113</v>
+        <v>7265098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648436</v>
+        <v>122648355</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535358</v>
+        <v>535896</v>
       </c>
       <c r="R7" t="n">
-        <v>7264941</v>
+        <v>7264601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648468</v>
+        <v>122648427</v>
       </c>
       <c r="B8" t="n">
-        <v>90966</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535007</v>
+        <v>534208</v>
       </c>
       <c r="R8" t="n">
-        <v>7265120</v>
+        <v>7265114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648355</v>
+        <v>122648466</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>74868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535896</v>
+        <v>534360</v>
       </c>
       <c r="R9" t="n">
-        <v>7264601</v>
+        <v>7265163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648390</v>
+        <v>122648475</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535573</v>
+        <v>534909</v>
       </c>
       <c r="R10" t="n">
-        <v>7264817</v>
+        <v>7265136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,6 +1601,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1618,7 +1623,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648464</v>
+        <v>122648398</v>
       </c>
       <c r="B11" t="n">
-        <v>79882</v>
+        <v>8430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534978</v>
+        <v>535550</v>
       </c>
       <c r="R11" t="n">
-        <v>7265116</v>
+        <v>7264828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648461</v>
+        <v>122648470</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>74868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534980</v>
+        <v>534374</v>
       </c>
       <c r="R12" t="n">
-        <v>7265114</v>
+        <v>7265137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648417</v>
+        <v>122648465</v>
       </c>
       <c r="B13" t="n">
-        <v>91243</v>
+        <v>74675</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535039</v>
+        <v>534361</v>
       </c>
       <c r="R13" t="n">
-        <v>7265098</v>
+        <v>7265171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648492</v>
+        <v>122648479</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>91890</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534466</v>
+        <v>534384</v>
       </c>
       <c r="R14" t="n">
-        <v>7265134</v>
+        <v>7265135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648455</v>
+        <v>122648428</v>
       </c>
       <c r="B15" t="n">
-        <v>91397</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535016</v>
+        <v>534215</v>
       </c>
       <c r="R15" t="n">
-        <v>7265112</v>
+        <v>7265115</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2153,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648426</v>
+        <v>122648418</v>
       </c>
       <c r="B16" t="n">
-        <v>77709</v>
+        <v>92266</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534205</v>
+        <v>534203</v>
       </c>
       <c r="R16" t="n">
-        <v>7265119</v>
+        <v>7265101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648456</v>
+        <v>122648474</v>
       </c>
       <c r="B17" t="n">
-        <v>91243</v>
+        <v>82553</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535016</v>
+        <v>534908</v>
       </c>
       <c r="R17" t="n">
-        <v>7265101</v>
+        <v>7265138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648453</v>
+        <v>122648403</v>
       </c>
       <c r="B18" t="n">
-        <v>91397</v>
+        <v>74847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535037</v>
+        <v>534162</v>
       </c>
       <c r="R18" t="n">
-        <v>7265096</v>
+        <v>7265113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648324</v>
+        <v>122648396</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2498,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535921</v>
+        <v>534129</v>
       </c>
       <c r="R19" t="n">
-        <v>7264587</v>
+        <v>7265112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2560,11 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2572,7 +2582,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648466</v>
+        <v>122648464</v>
       </c>
       <c r="B20" t="n">
-        <v>74868</v>
+        <v>79882</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2605,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534360</v>
+        <v>534978</v>
       </c>
       <c r="R20" t="n">
-        <v>7265163</v>
+        <v>7265116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2688,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648462</v>
+        <v>122648478</v>
       </c>
       <c r="B21" t="n">
-        <v>91890</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534952</v>
+        <v>534371</v>
       </c>
       <c r="R21" t="n">
-        <v>7265120</v>
+        <v>7265136</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2794,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648479</v>
+        <v>122648456</v>
       </c>
       <c r="B22" t="n">
-        <v>91890</v>
+        <v>91243</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R22" t="n">
-        <v>7265135</v>
+        <v>7265101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2900,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2901,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648398</v>
+        <v>122648483</v>
       </c>
       <c r="B23" t="n">
-        <v>8430</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2923,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535550</v>
+        <v>534458</v>
       </c>
       <c r="R23" t="n">
-        <v>7264828</v>
+        <v>7265138</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +3006,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3007,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648399</v>
+        <v>122648455</v>
       </c>
       <c r="B24" t="n">
-        <v>74855</v>
+        <v>91397</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3029,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3047,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535550</v>
+        <v>535016</v>
       </c>
       <c r="R24" t="n">
-        <v>7264829</v>
+        <v>7265112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648396</v>
+        <v>122648426</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3153,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534129</v>
+        <v>534205</v>
       </c>
       <c r="R25" t="n">
-        <v>7265112</v>
+        <v>7265119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,11 +3199,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3224,10 +3229,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648418</v>
+        <v>122648447</v>
       </c>
       <c r="B26" t="n">
-        <v>92266</v>
+        <v>90948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3241,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3264,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534203</v>
+        <v>535157</v>
       </c>
       <c r="R26" t="n">
-        <v>7265101</v>
+        <v>7265060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,7 +3324,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648427</v>
+        <v>122648453</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>91397</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3342,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534208</v>
+        <v>535037</v>
       </c>
       <c r="R27" t="n">
-        <v>7265114</v>
+        <v>7265096</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3430,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3436,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648465</v>
+        <v>122648462</v>
       </c>
       <c r="B28" t="n">
-        <v>74675</v>
+        <v>91890</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3476,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534361</v>
+        <v>534952</v>
       </c>
       <c r="R28" t="n">
-        <v>7265171</v>
+        <v>7265120</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3536,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3542,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648475</v>
+        <v>122648468</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90966</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,21 +3563,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534909</v>
+        <v>535007</v>
       </c>
       <c r="R29" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,11 +3623,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648447</v>
+        <v>122648324</v>
       </c>
       <c r="B30" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3669,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535157</v>
+        <v>535921</v>
       </c>
       <c r="R30" t="n">
-        <v>7265060</v>
+        <v>7264587</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648474</v>
+        <v>122648390</v>
       </c>
       <c r="B31" t="n">
-        <v>82553</v>
+        <v>90966</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534908</v>
+        <v>535573</v>
       </c>
       <c r="R31" t="n">
-        <v>7265138</v>
+        <v>7264817</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648470</v>
+        <v>122648461</v>
       </c>
       <c r="B32" t="n">
-        <v>74868</v>
+        <v>90970</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534374</v>
+        <v>534980</v>
       </c>
       <c r="R32" t="n">
-        <v>7265137</v>
+        <v>7265114</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122648467</v>
+        <v>122648399</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534384</v>
+        <v>535550</v>
       </c>
       <c r="R2" t="n">
-        <v>7265120</v>
+        <v>7264829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122648399</v>
+        <v>122648412</v>
       </c>
       <c r="B3" t="n">
-        <v>74855</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535550</v>
+        <v>534196</v>
       </c>
       <c r="R3" t="n">
-        <v>7264829</v>
+        <v>7265090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122648436</v>
+        <v>122648426</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535358</v>
+        <v>534205</v>
       </c>
       <c r="R4" t="n">
-        <v>7264941</v>
+        <v>7265119</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122648492</v>
+        <v>122648417</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534466</v>
+        <v>535039</v>
       </c>
       <c r="R5" t="n">
-        <v>7265134</v>
+        <v>7265098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122648417</v>
+        <v>122648456</v>
       </c>
       <c r="B6" t="n">
-        <v>91243</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,12 +1099,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535039</v>
+        <v>535016</v>
       </c>
       <c r="R6" t="n">
-        <v>7265098</v>
+        <v>7265101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122648355</v>
+        <v>122648312</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535896</v>
+        <v>534091</v>
       </c>
       <c r="R7" t="n">
-        <v>7264601</v>
+        <v>7265083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122648427</v>
+        <v>122648428</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534208</v>
+        <v>534215</v>
       </c>
       <c r="R8" t="n">
-        <v>7265114</v>
+        <v>7265115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122648466</v>
+        <v>122648447</v>
       </c>
       <c r="B9" t="n">
-        <v>74868</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534360</v>
+        <v>535157</v>
       </c>
       <c r="R9" t="n">
-        <v>7265163</v>
+        <v>7265060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122648475</v>
+        <v>122648467</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534909</v>
+        <v>534384</v>
       </c>
       <c r="R10" t="n">
-        <v>7265136</v>
+        <v>7265120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,11 +1556,6 @@
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122648398</v>
+        <v>122648390</v>
       </c>
       <c r="B11" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535550</v>
+        <v>535573</v>
       </c>
       <c r="R11" t="n">
-        <v>7264828</v>
+        <v>7264817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122648470</v>
+        <v>122648468</v>
       </c>
       <c r="B12" t="n">
-        <v>74868</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534374</v>
+        <v>535007</v>
       </c>
       <c r="R12" t="n">
-        <v>7265137</v>
+        <v>7265120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1835,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1846,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122648465</v>
+        <v>122648453</v>
       </c>
       <c r="B13" t="n">
-        <v>74675</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534361</v>
+        <v>535037</v>
       </c>
       <c r="R13" t="n">
-        <v>7265171</v>
+        <v>7265096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1952,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122648479</v>
+        <v>122648455</v>
       </c>
       <c r="B14" t="n">
-        <v>91890</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534384</v>
+        <v>535016</v>
       </c>
       <c r="R14" t="n">
-        <v>7265135</v>
+        <v>7265112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +1977,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2058,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122648428</v>
+        <v>122648474</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534215</v>
+        <v>534908</v>
       </c>
       <c r="R15" t="n">
-        <v>7265115</v>
+        <v>7265138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2164,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122648418</v>
+        <v>122648414</v>
       </c>
       <c r="B16" t="n">
-        <v>92266</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534203</v>
+        <v>534194</v>
       </c>
       <c r="R16" t="n">
-        <v>7265101</v>
+        <v>7265088</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122648474</v>
+        <v>122648466</v>
       </c>
       <c r="B17" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534908</v>
+        <v>534360</v>
       </c>
       <c r="R17" t="n">
-        <v>7265138</v>
+        <v>7265163</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2376,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122648403</v>
+        <v>122648470</v>
       </c>
       <c r="B18" t="n">
-        <v>74847</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2416,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534162</v>
+        <v>534374</v>
       </c>
       <c r="R18" t="n">
-        <v>7265113</v>
+        <v>7265137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122648396</v>
+        <v>122648498</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534129</v>
+        <v>534482</v>
       </c>
       <c r="R19" t="n">
-        <v>7265112</v>
+        <v>7265155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,11 +2463,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackmärke på grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122648464</v>
+        <v>122648462</v>
       </c>
       <c r="B20" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534978</v>
+        <v>534952</v>
       </c>
       <c r="R20" t="n">
-        <v>7265116</v>
+        <v>7265120</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,37 +2594,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122648478</v>
+        <v>122648479</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534371</v>
+        <v>534384</v>
       </c>
       <c r="R21" t="n">
-        <v>7265136</v>
+        <v>7265135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,15 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122648456</v>
+        <v>122648418</v>
       </c>
       <c r="B22" t="n">
-        <v>91243</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,7 +2730,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535016</v>
+        <v>534203</v>
       </c>
       <c r="R22" t="n">
         <v>7265101</v>
@@ -2900,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2911,19 +2796,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122648483</v>
+        <v>122648324</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2951,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534458</v>
+        <v>535921</v>
       </c>
       <c r="R23" t="n">
-        <v>7265138</v>
+        <v>7264587</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,7 +2886,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Lundin</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3017,15 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122648455</v>
+        <v>122648483</v>
       </c>
       <c r="B24" t="n">
-        <v>91397</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535016</v>
+        <v>534458</v>
       </c>
       <c r="R24" t="n">
-        <v>7265112</v>
+        <v>7265138</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +2987,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Magnus Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3123,37 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122648426</v>
+        <v>122648465</v>
       </c>
       <c r="B25" t="n">
-        <v>77709</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534205</v>
+        <v>534361</v>
       </c>
       <c r="R25" t="n">
-        <v>7265119</v>
+        <v>7265171</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,37 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122648447</v>
+        <v>122648391</v>
       </c>
       <c r="B26" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3269,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535157</v>
+        <v>534098</v>
       </c>
       <c r="R26" t="n">
-        <v>7265060</v>
+        <v>7265104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,37 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122648453</v>
+        <v>122648403</v>
       </c>
       <c r="B27" t="n">
-        <v>91397</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535037</v>
+        <v>534162</v>
       </c>
       <c r="R27" t="n">
-        <v>7265096</v>
+        <v>7265113</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3441,37 +3301,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122648462</v>
+        <v>122648427</v>
       </c>
       <c r="B28" t="n">
-        <v>91890</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3481,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534952</v>
+        <v>534208</v>
       </c>
       <c r="R28" t="n">
-        <v>7265120</v>
+        <v>7265114</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3391,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,15 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122648468</v>
+        <v>122648492</v>
       </c>
       <c r="B29" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3563,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3587,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535007</v>
+        <v>534466</v>
       </c>
       <c r="R29" t="n">
-        <v>7265120</v>
+        <v>7265134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3642,7 +3492,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3653,15 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122648324</v>
+        <v>122648499</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3693,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535921</v>
+        <v>534482</v>
       </c>
       <c r="R30" t="n">
-        <v>7264587</v>
+        <v>7265155</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3593,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sam Keith</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,37 +3604,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122648390</v>
+        <v>122648436</v>
       </c>
       <c r="B31" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3799,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535573</v>
+        <v>535358</v>
       </c>
       <c r="R31" t="n">
-        <v>7264817</v>
+        <v>7264941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,37 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122648461</v>
+        <v>122648464</v>
       </c>
       <c r="B32" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534980</v>
+        <v>534978</v>
       </c>
       <c r="R32" t="n">
-        <v>7265114</v>
+        <v>7265116</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,6 +3799,521 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122648396</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>534129</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7265112</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackmärke på grov gran.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122648475</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>534909</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7265136</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122648353</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>535867</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7264588</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122648398</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>535550</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7264828</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122648389</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>534106</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7265108</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4400,10 +4400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122648389</v>
+        <v>135572908</v>
       </c>
       <c r="B37" t="n">
-        <v>80398</v>
+        <v>106396</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229748</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dikanäs, Ly lm</t>
+          <t>Gardvik, 2,0 km ONO, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534106</v>
+        <v>534299</v>
       </c>
       <c r="R37" t="n">
-        <v>7265108</v>
+        <v>7264928</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,20 +4485,122 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Gunnar Janson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135572908</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122648389</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dikanäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>534106</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7265108</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Mika Thunell</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Rickard Gustafsson</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122648389</t>
         </is>
@@ -4542,6 +4644,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -4403,7 +4403,7 @@
         <v>135572908</v>
       </c>
       <c r="B37" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -4403,7 +4403,7 @@
         <v>135572908</v>
       </c>
       <c r="B37" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -4403,7 +4403,7 @@
         <v>135572908</v>
       </c>
       <c r="B37" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25126-2023 artfynd.xlsx
+++ b/artfynd/A 25126-2023 artfynd.xlsx
@@ -4403,7 +4403,7 @@
         <v>135572908</v>
       </c>
       <c r="B37" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
